--- a/research/traditional_assets/database/data/oman/oman_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_oil_gas_distribution.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08923564184996283</v>
+        <v>0.08914003838718787</v>
       </c>
       <c r="C2">
-        <v>2897.781269736526</v>
+        <v>2878.769300685027</v>
       </c>
       <c r="D2">
-        <v>2792.081269736526</v>
+        <v>2798.240300685027</v>
       </c>
       <c r="E2">
-        <v>-964.8</v>
+        <v>-939.6289999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>25.171</v>
       </c>
       <c r="G2">
         <v>105.7</v>
@@ -1445,28 +1445,28 @@
         <v>253.886</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.2661013</v>
       </c>
       <c r="N2">
-        <v>253.886</v>
+        <v>252.6198987</v>
       </c>
       <c r="O2">
-        <v>38.0829</v>
+        <v>37.892984805</v>
       </c>
       <c r="P2">
-        <v>215.8031</v>
+        <v>214.726913895</v>
       </c>
       <c r="Q2">
-        <v>216.2921</v>
+        <v>215.215913895</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08923564184996283</v>
+        <v>0.0896085741284726</v>
       </c>
       <c r="T2">
-        <v>0.5661120226706918</v>
+        <v>0.5709725804410967</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>200.5258189056437</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08914003838718787</v>
+        <v>0.08904443492441294</v>
       </c>
       <c r="C3">
-        <v>2878.769300685027</v>
+        <v>2859.784564024794</v>
       </c>
       <c r="D3">
-        <v>2798.240300685027</v>
+        <v>2804.426564024794</v>
       </c>
       <c r="E3">
-        <v>-939.6289999999999</v>
+        <v>-914.458</v>
       </c>
       <c r="F3">
-        <v>25.171</v>
+        <v>50.342</v>
       </c>
       <c r="G3">
         <v>105.7</v>
@@ -1527,28 +1527,28 @@
         <v>253.886</v>
       </c>
       <c r="M3">
-        <v>1.2661013</v>
+        <v>2.5322026</v>
       </c>
       <c r="N3">
-        <v>252.6198987</v>
+        <v>251.3537974</v>
       </c>
       <c r="O3">
-        <v>37.892984805</v>
+        <v>37.70306961</v>
       </c>
       <c r="P3">
-        <v>214.726913895</v>
+        <v>213.65072779</v>
       </c>
       <c r="Q3">
-        <v>215.215913895</v>
+        <v>214.13972779</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0896085741284726</v>
+        <v>0.08998911726980913</v>
       </c>
       <c r="T3">
-        <v>0.5709725804410967</v>
+        <v>0.5759323332680406</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>200.5258189056437</v>
+        <v>100.2629094528218</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08904443492441294</v>
+        <v>0.088948831461638</v>
       </c>
       <c r="C4">
-        <v>2859.784564024794</v>
+        <v>2840.827240769601</v>
       </c>
       <c r="D4">
-        <v>2804.426564024794</v>
+        <v>2810.640240769601</v>
       </c>
       <c r="E4">
-        <v>-914.458</v>
+        <v>-889.2869999999999</v>
       </c>
       <c r="F4">
-        <v>50.342</v>
+        <v>75.51299999999999</v>
       </c>
       <c r="G4">
         <v>105.7</v>
@@ -1609,28 +1609,28 @@
         <v>253.886</v>
       </c>
       <c r="M4">
-        <v>2.5322026</v>
+        <v>3.798303899999999</v>
       </c>
       <c r="N4">
-        <v>251.3537974</v>
+        <v>250.0876961</v>
       </c>
       <c r="O4">
-        <v>37.70306961</v>
+        <v>37.513154415</v>
       </c>
       <c r="P4">
-        <v>213.65072779</v>
+        <v>212.574541685</v>
       </c>
       <c r="Q4">
-        <v>214.13972779</v>
+        <v>213.063541685</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08998911726980913</v>
+        <v>0.09037750666148248</v>
       </c>
       <c r="T4">
-        <v>0.5759323332680406</v>
+        <v>0.5809943490398698</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>100.2629094528218</v>
+        <v>66.84193963521456</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.088948831461638</v>
+        <v>0.08885322799886305</v>
       </c>
       <c r="C5">
-        <v>2840.827240769601</v>
+        <v>2821.897513541048</v>
       </c>
       <c r="D5">
-        <v>2810.640240769601</v>
+        <v>2816.881513541048</v>
       </c>
       <c r="E5">
-        <v>-889.2869999999999</v>
+        <v>-864.116</v>
       </c>
       <c r="F5">
-        <v>75.51299999999999</v>
+        <v>100.684</v>
       </c>
       <c r="G5">
         <v>105.7</v>
@@ -1691,28 +1691,28 @@
         <v>253.886</v>
       </c>
       <c r="M5">
-        <v>3.798303899999999</v>
+        <v>5.064405199999999</v>
       </c>
       <c r="N5">
-        <v>250.0876961</v>
+        <v>248.8215948</v>
       </c>
       <c r="O5">
-        <v>37.513154415</v>
+        <v>37.32323922</v>
       </c>
       <c r="P5">
-        <v>212.574541685</v>
+        <v>211.49835558</v>
       </c>
       <c r="Q5">
-        <v>213.063541685</v>
+        <v>211.98735558</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09037750666148248</v>
+        <v>0.09077398749881568</v>
       </c>
       <c r="T5">
-        <v>0.5809943490398698</v>
+        <v>0.5861618234736121</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>66.84193963521456</v>
+        <v>50.13145472641092</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08885322799886305</v>
+        <v>0.0887576245360881</v>
       </c>
       <c r="C6">
-        <v>2821.897513541048</v>
+        <v>2802.995566586452</v>
       </c>
       <c r="D6">
-        <v>2816.881513541048</v>
+        <v>2823.150566586452</v>
       </c>
       <c r="E6">
-        <v>-864.116</v>
+        <v>-838.9449999999999</v>
       </c>
       <c r="F6">
-        <v>100.684</v>
+        <v>125.855</v>
       </c>
       <c r="G6">
         <v>105.7</v>
@@ -1773,28 +1773,28 @@
         <v>253.886</v>
       </c>
       <c r="M6">
-        <v>5.064405199999999</v>
+        <v>6.3305065</v>
       </c>
       <c r="N6">
-        <v>248.8215948</v>
+        <v>247.5554935</v>
       </c>
       <c r="O6">
-        <v>37.32323922</v>
+        <v>37.13332402499999</v>
       </c>
       <c r="P6">
-        <v>211.49835558</v>
+        <v>210.422169475</v>
       </c>
       <c r="Q6">
-        <v>211.98735558</v>
+        <v>210.911169475</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09077398749881568</v>
+        <v>0.09117881530114538</v>
       </c>
       <c r="T6">
-        <v>0.5861618234736121</v>
+        <v>0.5914380868428017</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>50.13145472641092</v>
+        <v>40.10516378112872</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0887576245360881</v>
+        <v>0.08866202107331317</v>
       </c>
       <c r="C7">
-        <v>2802.995566586452</v>
+        <v>2784.121585796979</v>
       </c>
       <c r="D7">
-        <v>2823.150566586452</v>
+        <v>2829.447585796979</v>
       </c>
       <c r="E7">
-        <v>-838.9449999999999</v>
+        <v>-813.7739999999999</v>
       </c>
       <c r="F7">
-        <v>125.855</v>
+        <v>151.026</v>
       </c>
       <c r="G7">
         <v>105.7</v>
@@ -1855,28 +1855,28 @@
         <v>253.886</v>
       </c>
       <c r="M7">
-        <v>6.3305065</v>
+        <v>7.5966078</v>
       </c>
       <c r="N7">
-        <v>247.5554935</v>
+        <v>246.2893922</v>
       </c>
       <c r="O7">
-        <v>37.13332402499999</v>
+        <v>36.94340883</v>
       </c>
       <c r="P7">
-        <v>210.422169475</v>
+        <v>209.34598337</v>
       </c>
       <c r="Q7">
-        <v>210.911169475</v>
+        <v>209.83498337</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09117881530114538</v>
+        <v>0.09159225646097145</v>
       </c>
       <c r="T7">
-        <v>0.5914380868428017</v>
+        <v>0.59682661113474</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>40.10516378112872</v>
+        <v>33.42096981760727</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08866202107331317</v>
+        <v>0.08856641761053823</v>
       </c>
       <c r="C8">
-        <v>2784.121585796979</v>
+        <v>2765.275758726023</v>
       </c>
       <c r="D8">
-        <v>2829.447585796979</v>
+        <v>2835.772758726024</v>
       </c>
       <c r="E8">
-        <v>-813.774</v>
+        <v>-788.603</v>
       </c>
       <c r="F8">
-        <v>151.026</v>
+        <v>176.197</v>
       </c>
       <c r="G8">
         <v>105.7</v>
@@ -1937,28 +1937,28 @@
         <v>253.886</v>
       </c>
       <c r="M8">
-        <v>7.596607799999998</v>
+        <v>8.862709099999998</v>
       </c>
       <c r="N8">
-        <v>246.2893922</v>
+        <v>245.0232909</v>
       </c>
       <c r="O8">
-        <v>36.94340883</v>
+        <v>36.753493635</v>
       </c>
       <c r="P8">
-        <v>209.34598337</v>
+        <v>208.269797265</v>
       </c>
       <c r="Q8">
-        <v>209.83498337</v>
+        <v>208.758797265</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09159225646097145</v>
+        <v>0.09201458882853572</v>
       </c>
       <c r="T8">
-        <v>0.59682661113474</v>
+        <v>0.6023310176695157</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>33.42096981760729</v>
+        <v>28.6465455579491</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08856641761053823</v>
+        <v>0.08847081414776328</v>
       </c>
       <c r="C9">
-        <v>2765.275758726023</v>
+        <v>2746.458274607821</v>
       </c>
       <c r="D9">
-        <v>2835.772758726024</v>
+        <v>2842.126274607821</v>
       </c>
       <c r="E9">
-        <v>-788.603</v>
+        <v>-763.432</v>
       </c>
       <c r="F9">
-        <v>176.197</v>
+        <v>201.368</v>
       </c>
       <c r="G9">
         <v>105.7</v>
@@ -2019,28 +2019,28 @@
         <v>253.886</v>
       </c>
       <c r="M9">
-        <v>8.8627091</v>
+        <v>10.1288104</v>
       </c>
       <c r="N9">
-        <v>245.0232909</v>
+        <v>243.7571896</v>
       </c>
       <c r="O9">
-        <v>36.753493635</v>
+        <v>36.56357844</v>
       </c>
       <c r="P9">
-        <v>208.269797265</v>
+        <v>207.19361116</v>
       </c>
       <c r="Q9">
-        <v>208.758797265</v>
+        <v>207.68261116</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09201458882853572</v>
+        <v>0.0924461023345253</v>
       </c>
       <c r="T9">
-        <v>0.6023310176695157</v>
+        <v>0.6079550852159169</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.64654555794909</v>
+        <v>25.06572736320546</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08847081414776328</v>
+        <v>0.08837521068498833</v>
       </c>
       <c r="C10">
-        <v>2746.458274607821</v>
+        <v>2727.669324376327</v>
       </c>
       <c r="D10">
-        <v>2842.126274607821</v>
+        <v>2848.508324376327</v>
       </c>
       <c r="E10">
-        <v>-763.432</v>
+        <v>-738.261</v>
       </c>
       <c r="F10">
-        <v>201.368</v>
+        <v>226.539</v>
       </c>
       <c r="G10">
         <v>105.7</v>
@@ -2101,28 +2101,28 @@
         <v>253.886</v>
       </c>
       <c r="M10">
-        <v>10.1288104</v>
+        <v>11.3949117</v>
       </c>
       <c r="N10">
-        <v>243.7571896</v>
+        <v>242.4910883</v>
       </c>
       <c r="O10">
-        <v>36.56357844</v>
+        <v>36.373663245</v>
       </c>
       <c r="P10">
-        <v>207.19361116</v>
+        <v>206.117425055</v>
       </c>
       <c r="Q10">
-        <v>207.68261116</v>
+        <v>206.606425055</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0924461023345253</v>
+        <v>0.09288709965383332</v>
       </c>
       <c r="T10">
-        <v>0.6079550852159169</v>
+        <v>0.6137027586424587</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.06572736320546</v>
+        <v>22.28064654507152</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08837521068498833</v>
+        <v>0.08827960722221341</v>
       </c>
       <c r="C11">
-        <v>2727.669324376327</v>
+        <v>2708.909100684332</v>
       </c>
       <c r="D11">
-        <v>2848.508324376327</v>
+        <v>2854.919100684333</v>
       </c>
       <c r="E11">
-        <v>-738.261</v>
+        <v>-713.0899999999999</v>
       </c>
       <c r="F11">
-        <v>226.539</v>
+        <v>251.71</v>
       </c>
       <c r="G11">
         <v>105.7</v>
@@ -2183,28 +2183,28 @@
         <v>253.886</v>
       </c>
       <c r="M11">
-        <v>11.3949117</v>
+        <v>12.661013</v>
       </c>
       <c r="N11">
-        <v>242.4910883</v>
+        <v>241.224987</v>
       </c>
       <c r="O11">
-        <v>36.373663245</v>
+        <v>36.18374805</v>
       </c>
       <c r="P11">
-        <v>206.117425055</v>
+        <v>205.04123895</v>
       </c>
       <c r="Q11">
-        <v>206.606425055</v>
+        <v>205.53023895</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09288709965383332</v>
+        <v>0.09333789691357045</v>
       </c>
       <c r="T11">
-        <v>0.6137027586424587</v>
+        <v>0.6195781581451462</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.28064654507152</v>
+        <v>20.05258189056437</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08827960722221341</v>
+        <v>0.08818400375943845</v>
       </c>
       <c r="C12">
-        <v>2708.909100684332</v>
+        <v>2690.177797922869</v>
       </c>
       <c r="D12">
-        <v>2854.919100684333</v>
+        <v>2861.358797922869</v>
       </c>
       <c r="E12">
-        <v>-713.0899999999999</v>
+        <v>-687.919</v>
       </c>
       <c r="F12">
-        <v>251.71</v>
+        <v>276.881</v>
       </c>
       <c r="G12">
         <v>105.7</v>
@@ -2265,28 +2265,28 @@
         <v>253.886</v>
       </c>
       <c r="M12">
-        <v>12.661013</v>
+        <v>13.9271143</v>
       </c>
       <c r="N12">
-        <v>241.224987</v>
+        <v>239.9588857</v>
       </c>
       <c r="O12">
-        <v>36.18374805</v>
+        <v>35.993832855</v>
       </c>
       <c r="P12">
-        <v>205.04123895</v>
+        <v>203.965052845</v>
       </c>
       <c r="Q12">
-        <v>205.53023895</v>
+        <v>204.454052845</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09333789691357045</v>
+        <v>0.09379882444880724</v>
       </c>
       <c r="T12">
-        <v>0.6195781581451462</v>
+        <v>0.625585589097332</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.05258189056437</v>
+        <v>18.22961990051306</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08818400375943845</v>
+        <v>0.0880884002966635</v>
       </c>
       <c r="C13">
-        <v>2690.177797922869</v>
+        <v>2671.475612240837</v>
       </c>
       <c r="D13">
-        <v>2861.358797922869</v>
+        <v>2867.827612240837</v>
       </c>
       <c r="E13">
-        <v>-687.919</v>
+        <v>-662.748</v>
       </c>
       <c r="F13">
-        <v>276.881</v>
+        <v>302.052</v>
       </c>
       <c r="G13">
         <v>105.7</v>
@@ -2347,28 +2347,28 @@
         <v>253.886</v>
       </c>
       <c r="M13">
-        <v>13.9271143</v>
+        <v>15.1932156</v>
       </c>
       <c r="N13">
-        <v>239.9588857</v>
+        <v>238.6927844</v>
       </c>
       <c r="O13">
-        <v>35.993832855</v>
+        <v>35.80391766</v>
       </c>
       <c r="P13">
-        <v>203.965052845</v>
+        <v>202.88886674</v>
       </c>
       <c r="Q13">
-        <v>204.454052845</v>
+        <v>203.37786674</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09379882444880724</v>
+        <v>0.09427022760984488</v>
       </c>
       <c r="T13">
-        <v>0.625585589097332</v>
+        <v>0.6317295525711584</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.22961990051306</v>
+        <v>16.71048490880364</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0880884002966635</v>
+        <v>0.08799279683388855</v>
       </c>
       <c r="C14">
-        <v>2671.475612240837</v>
+        <v>2652.802741564931</v>
       </c>
       <c r="D14">
-        <v>2867.827612240837</v>
+        <v>2874.325741564931</v>
       </c>
       <c r="E14">
-        <v>-662.748</v>
+        <v>-637.577</v>
       </c>
       <c r="F14">
-        <v>302.052</v>
+        <v>327.223</v>
       </c>
       <c r="G14">
         <v>105.7</v>
@@ -2429,28 +2429,28 @@
         <v>253.886</v>
       </c>
       <c r="M14">
-        <v>15.1932156</v>
+        <v>16.4593169</v>
       </c>
       <c r="N14">
-        <v>238.6927844</v>
+        <v>237.4266831</v>
       </c>
       <c r="O14">
-        <v>35.80391766</v>
+        <v>35.614002465</v>
       </c>
       <c r="P14">
-        <v>202.88886674</v>
+        <v>201.812680635</v>
       </c>
       <c r="Q14">
-        <v>203.37786674</v>
+        <v>202.301680635</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09427022760984488</v>
+        <v>0.09475246762515926</v>
       </c>
       <c r="T14">
-        <v>0.6317295525711584</v>
+        <v>0.638014756584613</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.71048490880364</v>
+        <v>15.42506299274182</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08799279683388855</v>
+        <v>0.0878971933711136</v>
       </c>
       <c r="C15">
-        <v>2652.802741564931</v>
+        <v>2634.159385619828</v>
       </c>
       <c r="D15">
-        <v>2874.325741564931</v>
+        <v>2880.853385619828</v>
       </c>
       <c r="E15">
-        <v>-637.577</v>
+        <v>-612.4059999999999</v>
       </c>
       <c r="F15">
-        <v>327.223</v>
+        <v>352.394</v>
       </c>
       <c r="G15">
         <v>105.7</v>
@@ -2511,28 +2511,28 @@
         <v>253.886</v>
       </c>
       <c r="M15">
-        <v>16.4593169</v>
+        <v>17.7254182</v>
       </c>
       <c r="N15">
-        <v>237.4266831</v>
+        <v>236.1605818</v>
       </c>
       <c r="O15">
-        <v>35.614002465</v>
+        <v>35.42408726999999</v>
       </c>
       <c r="P15">
-        <v>201.812680635</v>
+        <v>200.73649453</v>
       </c>
       <c r="Q15">
-        <v>202.301680635</v>
+        <v>201.22549453</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09475246762515926</v>
+        <v>0.09524592252455071</v>
       </c>
       <c r="T15">
-        <v>0.638014756584613</v>
+        <v>0.6444461281332642</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.42506299274182</v>
+        <v>14.32327277897455</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0878971933711136</v>
+        <v>0.08780158990833865</v>
       </c>
       <c r="C16">
-        <v>2634.159385619828</v>
+        <v>2615.545745948644</v>
       </c>
       <c r="D16">
-        <v>2880.853385619828</v>
+        <v>2887.410745948644</v>
       </c>
       <c r="E16">
-        <v>-612.4059999999999</v>
+        <v>-587.2349999999999</v>
       </c>
       <c r="F16">
-        <v>352.394</v>
+        <v>377.5650000000001</v>
       </c>
       <c r="G16">
         <v>105.7</v>
@@ -2593,28 +2593,28 @@
         <v>253.886</v>
       </c>
       <c r="M16">
-        <v>17.7254182</v>
+        <v>18.9915195</v>
       </c>
       <c r="N16">
-        <v>236.1605818</v>
+        <v>234.8944805</v>
       </c>
       <c r="O16">
-        <v>35.42408726999999</v>
+        <v>35.234172075</v>
       </c>
       <c r="P16">
-        <v>200.73649453</v>
+        <v>199.660308425</v>
       </c>
       <c r="Q16">
-        <v>201.22549453</v>
+        <v>200.149308425</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09524592252455071</v>
+        <v>0.09575098812745725</v>
       </c>
       <c r="T16">
-        <v>0.6444461281332642</v>
+        <v>0.6510288260712955</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.32327277897455</v>
+        <v>13.36838792704291</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08780158990833865</v>
+        <v>0.08790998644556373</v>
       </c>
       <c r="C17">
-        <v>2615.545745948644</v>
+        <v>2582.942178217664</v>
       </c>
       <c r="D17">
-        <v>2887.410745948644</v>
+        <v>2879.978178217664</v>
       </c>
       <c r="E17">
-        <v>-587.2349999999999</v>
+        <v>-562.064</v>
       </c>
       <c r="F17">
-        <v>377.565</v>
+        <v>402.736</v>
       </c>
       <c r="G17">
         <v>105.7</v>
@@ -2675,45 +2675,45 @@
         <v>253.886</v>
       </c>
       <c r="M17">
-        <v>18.9915195</v>
+        <v>20.8617248</v>
       </c>
       <c r="N17">
-        <v>234.8944805</v>
+        <v>233.0242752</v>
       </c>
       <c r="O17">
-        <v>35.234172075</v>
+        <v>34.95364128</v>
       </c>
       <c r="P17">
-        <v>199.660308425</v>
+        <v>198.07063392</v>
       </c>
       <c r="Q17">
-        <v>200.149308425</v>
+        <v>198.55963392</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09575098812745725</v>
+        <v>0.09626807910186158</v>
       </c>
       <c r="T17">
-        <v>0.6510288260712955</v>
+        <v>0.6577682549126134</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.15</v>
       </c>
       <c r="W17">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.36838792704291</v>
+        <v>12.16994291862196</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08790998644556373</v>
+        <v>0.08782713298278877</v>
       </c>
       <c r="C18">
-        <v>2582.942178217664</v>
+        <v>2563.448847567115</v>
       </c>
       <c r="D18">
-        <v>2879.978178217664</v>
+        <v>2885.655847567115</v>
       </c>
       <c r="E18">
-        <v>-562.064</v>
+        <v>-536.8929999999999</v>
       </c>
       <c r="F18">
-        <v>402.736</v>
+        <v>427.907</v>
       </c>
       <c r="G18">
         <v>105.7</v>
@@ -2757,28 +2757,28 @@
         <v>253.886</v>
       </c>
       <c r="M18">
-        <v>20.8617248</v>
+        <v>22.1655826</v>
       </c>
       <c r="N18">
-        <v>233.0242752</v>
+        <v>231.7204174</v>
       </c>
       <c r="O18">
-        <v>34.95364128</v>
+        <v>34.75806261</v>
       </c>
       <c r="P18">
-        <v>198.07063392</v>
+        <v>196.96235479</v>
       </c>
       <c r="Q18">
-        <v>198.55963392</v>
+        <v>197.45135479</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09626807910186158</v>
+        <v>0.09679763009974551</v>
       </c>
       <c r="T18">
-        <v>0.6577682549126134</v>
+        <v>0.6646700796296255</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.16994291862196</v>
+        <v>11.4540639234089</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08782713298278877</v>
+        <v>0.08774427952001382</v>
       </c>
       <c r="C19">
-        <v>2563.448847567115</v>
+        <v>2543.977947368177</v>
       </c>
       <c r="D19">
-        <v>2885.655847567115</v>
+        <v>2891.355947368178</v>
       </c>
       <c r="E19">
-        <v>-536.8929999999999</v>
+        <v>-511.7219999999999</v>
       </c>
       <c r="F19">
-        <v>427.907</v>
+        <v>453.078</v>
       </c>
       <c r="G19">
         <v>105.7</v>
@@ -2839,28 +2839,28 @@
         <v>253.886</v>
       </c>
       <c r="M19">
-        <v>22.1655826</v>
+        <v>23.4694404</v>
       </c>
       <c r="N19">
-        <v>231.7204174</v>
+        <v>230.4165596</v>
       </c>
       <c r="O19">
-        <v>34.75806261</v>
+        <v>34.56248394</v>
       </c>
       <c r="P19">
-        <v>196.96235479</v>
+        <v>195.85407566</v>
       </c>
       <c r="Q19">
-        <v>197.45135479</v>
+        <v>196.34307566</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09679763009974551</v>
+        <v>0.09734009697562662</v>
       </c>
       <c r="T19">
-        <v>0.6646700796296255</v>
+        <v>0.6717402415348575</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.4540639234089</v>
+        <v>10.81772703877507</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08774427952001383</v>
+        <v>0.08766142605723889</v>
       </c>
       <c r="C20">
-        <v>2543.977947368176</v>
+        <v>2524.529610806034</v>
       </c>
       <c r="D20">
-        <v>2891.355947368176</v>
+        <v>2897.078610806034</v>
       </c>
       <c r="E20">
-        <v>-511.722</v>
+        <v>-486.551</v>
       </c>
       <c r="F20">
-        <v>453.078</v>
+        <v>478.249</v>
       </c>
       <c r="G20">
         <v>105.7</v>
@@ -2921,28 +2921,28 @@
         <v>253.886</v>
       </c>
       <c r="M20">
-        <v>23.4694404</v>
+        <v>24.7732982</v>
       </c>
       <c r="N20">
-        <v>230.4165596</v>
+        <v>229.1127018</v>
       </c>
       <c r="O20">
-        <v>34.56248394</v>
+        <v>34.36690527</v>
       </c>
       <c r="P20">
-        <v>195.85407566</v>
+        <v>194.74579653</v>
       </c>
       <c r="Q20">
-        <v>196.34307566</v>
+        <v>195.23479653</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09734009697562662</v>
+        <v>0.09789595809535664</v>
       </c>
       <c r="T20">
-        <v>0.6717402415348575</v>
+        <v>0.6789849753389841</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.81772703877507</v>
+        <v>10.2483729841027</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08766142605723889</v>
+        <v>0.08786757259446396</v>
       </c>
       <c r="C21">
-        <v>2524.529610806034</v>
+        <v>2485.161862887067</v>
       </c>
       <c r="D21">
-        <v>2897.078610806034</v>
+        <v>2882.881862887068</v>
       </c>
       <c r="E21">
-        <v>-486.551</v>
+        <v>-461.3799999999999</v>
       </c>
       <c r="F21">
-        <v>478.249</v>
+        <v>503.42</v>
       </c>
       <c r="G21">
         <v>105.7</v>
@@ -3003,45 +3003,45 @@
         <v>253.886</v>
       </c>
       <c r="M21">
-        <v>24.7732982</v>
+        <v>26.93297</v>
       </c>
       <c r="N21">
-        <v>229.1127018</v>
+        <v>226.95303</v>
       </c>
       <c r="O21">
-        <v>34.36690527</v>
+        <v>34.04295449999999</v>
       </c>
       <c r="P21">
-        <v>194.74579653</v>
+        <v>192.9100755</v>
       </c>
       <c r="Q21">
-        <v>195.23479653</v>
+        <v>193.3990755</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09789595809535664</v>
+        <v>0.09846571574307994</v>
       </c>
       <c r="T21">
-        <v>0.6789849753389841</v>
+        <v>0.6864108274882138</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.15</v>
       </c>
       <c r="W21">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>10.2483729841027</v>
+        <v>9.426587561639135</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08786757259446396</v>
+        <v>0.087799169131689</v>
       </c>
       <c r="C22">
-        <v>2485.161862887067</v>
+        <v>2464.686172491271</v>
       </c>
       <c r="D22">
-        <v>2882.881862887068</v>
+        <v>2887.577172491271</v>
       </c>
       <c r="E22">
-        <v>-461.3799999999999</v>
+        <v>-436.2089999999999</v>
       </c>
       <c r="F22">
-        <v>503.42</v>
+        <v>528.591</v>
       </c>
       <c r="G22">
         <v>105.7</v>
@@ -3085,28 +3085,28 @@
         <v>253.886</v>
       </c>
       <c r="M22">
-        <v>26.93297</v>
+        <v>28.2796185</v>
       </c>
       <c r="N22">
-        <v>226.95303</v>
+        <v>225.6063815</v>
       </c>
       <c r="O22">
-        <v>34.04295449999999</v>
+        <v>33.840957225</v>
       </c>
       <c r="P22">
-        <v>192.9100755</v>
+        <v>191.765424275</v>
       </c>
       <c r="Q22">
-        <v>193.3990755</v>
+        <v>192.254424275</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09846571574307994</v>
+        <v>0.09904989763504937</v>
       </c>
       <c r="T22">
-        <v>0.6864108274882138</v>
+        <v>0.6940246758943862</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.426587561639135</v>
+        <v>8.977702439656319</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.087799169131689</v>
+        <v>0.08773076566891405</v>
       </c>
       <c r="C23">
-        <v>2464.686172491271</v>
+        <v>2444.22580141677</v>
       </c>
       <c r="D23">
-        <v>2887.577172491271</v>
+        <v>2892.28780141677</v>
       </c>
       <c r="E23">
-        <v>-436.2089999999999</v>
+        <v>-411.038</v>
       </c>
       <c r="F23">
-        <v>528.591</v>
+        <v>553.7619999999999</v>
       </c>
       <c r="G23">
         <v>105.7</v>
@@ -3167,28 +3167,28 @@
         <v>253.886</v>
       </c>
       <c r="M23">
-        <v>28.2796185</v>
+        <v>29.626267</v>
       </c>
       <c r="N23">
-        <v>225.6063815</v>
+        <v>224.259733</v>
       </c>
       <c r="O23">
-        <v>33.840957225</v>
+        <v>33.63895995</v>
       </c>
       <c r="P23">
-        <v>191.765424275</v>
+        <v>190.62077305</v>
       </c>
       <c r="Q23">
-        <v>192.254424275</v>
+        <v>191.10977305</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09904989763504937</v>
+        <v>0.09964905854988981</v>
       </c>
       <c r="T23">
-        <v>0.6940246758943861</v>
+        <v>0.7018337511827679</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.977702439656319</v>
+        <v>8.56962505603558</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08773076566891405</v>
+        <v>0.08766236220613911</v>
       </c>
       <c r="C24">
-        <v>2444.22580141677</v>
+        <v>2423.780824759275</v>
       </c>
       <c r="D24">
-        <v>2892.28780141677</v>
+        <v>2897.013824759275</v>
       </c>
       <c r="E24">
-        <v>-411.038</v>
+        <v>-385.867</v>
       </c>
       <c r="F24">
-        <v>553.7619999999999</v>
+        <v>578.933</v>
       </c>
       <c r="G24">
         <v>105.7</v>
@@ -3249,28 +3249,28 @@
         <v>253.886</v>
       </c>
       <c r="M24">
-        <v>29.626267</v>
+        <v>30.9729155</v>
       </c>
       <c r="N24">
-        <v>224.259733</v>
+        <v>222.9130845</v>
       </c>
       <c r="O24">
-        <v>33.63895995</v>
+        <v>33.436962675</v>
       </c>
       <c r="P24">
-        <v>190.62077305</v>
+        <v>189.476121825</v>
       </c>
       <c r="Q24">
-        <v>191.10977305</v>
+        <v>189.965121825</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09964905854988981</v>
+        <v>0.100263782085895</v>
       </c>
       <c r="T24">
-        <v>0.7018337511827679</v>
+        <v>0.7098456595955233</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.56962505603558</v>
+        <v>8.197032662294902</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08766236220613911</v>
+        <v>0.08759395874336418</v>
       </c>
       <c r="C25">
-        <v>2423.780824759275</v>
+        <v>2403.35131810613</v>
       </c>
       <c r="D25">
-        <v>2897.013824759275</v>
+        <v>2901.75531810613</v>
       </c>
       <c r="E25">
-        <v>-385.867</v>
+        <v>-360.6959999999999</v>
       </c>
       <c r="F25">
-        <v>578.933</v>
+        <v>604.104</v>
       </c>
       <c r="G25">
         <v>105.7</v>
@@ -3331,28 +3331,28 @@
         <v>253.886</v>
       </c>
       <c r="M25">
-        <v>30.9729155</v>
+        <v>32.319564</v>
       </c>
       <c r="N25">
-        <v>222.9130845</v>
+        <v>221.566436</v>
       </c>
       <c r="O25">
-        <v>33.436962675</v>
+        <v>33.2349654</v>
       </c>
       <c r="P25">
-        <v>189.476121825</v>
+        <v>188.3314706</v>
       </c>
       <c r="Q25">
-        <v>189.965121825</v>
+        <v>188.8204706</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.100263782085895</v>
+        <v>0.1008946825570581</v>
       </c>
       <c r="T25">
-        <v>0.7098456595955233</v>
+        <v>0.7180684077033512</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.197032662294902</v>
+        <v>7.85548963469928</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08759395874336416</v>
+        <v>0.08769555528058921</v>
       </c>
       <c r="C26">
-        <v>2403.351318106131</v>
+        <v>2371.143574226749</v>
       </c>
       <c r="D26">
-        <v>2901.755318106131</v>
+        <v>2894.71857422675</v>
       </c>
       <c r="E26">
-        <v>-360.696</v>
+        <v>-335.525</v>
       </c>
       <c r="F26">
-        <v>604.1039999999999</v>
+        <v>629.275</v>
       </c>
       <c r="G26">
         <v>105.7</v>
@@ -3413,45 +3413,45 @@
         <v>253.886</v>
       </c>
       <c r="M26">
-        <v>32.31956399999999</v>
+        <v>34.1696325</v>
       </c>
       <c r="N26">
-        <v>221.566436</v>
+        <v>219.7163675</v>
       </c>
       <c r="O26">
-        <v>33.2349654</v>
+        <v>32.957455125</v>
       </c>
       <c r="P26">
-        <v>188.3314706</v>
+        <v>186.758912375</v>
       </c>
       <c r="Q26">
-        <v>188.8204706</v>
+        <v>187.247912375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1008946825570581</v>
+        <v>0.1015424070407856</v>
       </c>
       <c r="T26">
-        <v>0.7180684077033512</v>
+        <v>0.7265104290940545</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.15</v>
       </c>
       <c r="W26">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.855489634699282</v>
+        <v>7.430164781549816</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08769555528058921</v>
+        <v>0.08763395181781429</v>
       </c>
       <c r="C27">
-        <v>2371.143574226749</v>
+        <v>2350.235252749397</v>
       </c>
       <c r="D27">
-        <v>2894.71857422675</v>
+        <v>2898.981252749397</v>
       </c>
       <c r="E27">
-        <v>-335.525</v>
+        <v>-310.3539999999999</v>
       </c>
       <c r="F27">
-        <v>629.275</v>
+        <v>654.446</v>
       </c>
       <c r="G27">
         <v>105.7</v>
@@ -3495,28 +3495,28 @@
         <v>253.886</v>
       </c>
       <c r="M27">
-        <v>34.1696325</v>
+        <v>35.5364178</v>
       </c>
       <c r="N27">
-        <v>219.7163675</v>
+        <v>218.3495822</v>
       </c>
       <c r="O27">
-        <v>32.957455125</v>
+        <v>32.75243733</v>
       </c>
       <c r="P27">
-        <v>186.758912375</v>
+        <v>185.59714487</v>
       </c>
       <c r="Q27">
-        <v>187.247912375</v>
+        <v>186.08614487</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1015424070407856</v>
+        <v>0.1022076375916409</v>
       </c>
       <c r="T27">
-        <v>0.7265104290940545</v>
+        <v>0.735180613225047</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.430164781549816</v>
+        <v>7.144389213028669</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08763395181781429</v>
+        <v>0.08757234835503933</v>
       </c>
       <c r="C28">
-        <v>2350.235252749397</v>
+        <v>2329.339503979497</v>
       </c>
       <c r="D28">
-        <v>2898.981252749397</v>
+        <v>2903.256503979497</v>
       </c>
       <c r="E28">
-        <v>-310.3539999999999</v>
+        <v>-285.1829999999999</v>
       </c>
       <c r="F28">
-        <v>654.446</v>
+        <v>679.6170000000001</v>
       </c>
       <c r="G28">
         <v>105.7</v>
@@ -3577,28 +3577,28 @@
         <v>253.886</v>
       </c>
       <c r="M28">
-        <v>35.5364178</v>
+        <v>36.90320310000001</v>
       </c>
       <c r="N28">
-        <v>218.3495822</v>
+        <v>216.9827969</v>
       </c>
       <c r="O28">
-        <v>32.75243733</v>
+        <v>32.547419535</v>
       </c>
       <c r="P28">
-        <v>185.59714487</v>
+        <v>184.435377365</v>
       </c>
       <c r="Q28">
-        <v>186.08614487</v>
+        <v>184.924377365</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1022076375916409</v>
+        <v>0.1028910936370402</v>
       </c>
       <c r="T28">
-        <v>0.735180613225047</v>
+        <v>0.7440883366472998</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.144389213028669</v>
+        <v>6.879782205138717</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08757234835503933</v>
+        <v>0.08751074489226439</v>
       </c>
       <c r="C29">
-        <v>2329.339503979497</v>
+        <v>2308.456383623722</v>
       </c>
       <c r="D29">
-        <v>2903.256503979497</v>
+        <v>2907.544383623722</v>
       </c>
       <c r="E29">
-        <v>-285.1829999999999</v>
+        <v>-260.0119999999999</v>
       </c>
       <c r="F29">
-        <v>679.6170000000001</v>
+        <v>704.788</v>
       </c>
       <c r="G29">
         <v>105.7</v>
@@ -3659,28 +3659,28 @@
         <v>253.886</v>
       </c>
       <c r="M29">
-        <v>36.90320310000001</v>
+        <v>38.2699884</v>
       </c>
       <c r="N29">
-        <v>216.9827969</v>
+        <v>215.6160116</v>
       </c>
       <c r="O29">
-        <v>32.547419535</v>
+        <v>32.34240173999999</v>
       </c>
       <c r="P29">
-        <v>184.435377365</v>
+        <v>183.27360986</v>
       </c>
       <c r="Q29">
-        <v>184.924377365</v>
+        <v>183.76260986</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1028910936370402</v>
+        <v>0.1035935345725894</v>
       </c>
       <c r="T29">
-        <v>0.7440883366472998</v>
+        <v>0.7532434968312817</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.879782205138717</v>
+        <v>6.634075697812335</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08751074489226439</v>
+        <v>0.08744914142948947</v>
       </c>
       <c r="C30">
-        <v>2308.456383623722</v>
+        <v>2287.585947718332</v>
       </c>
       <c r="D30">
-        <v>2907.544383623722</v>
+        <v>2911.844947718333</v>
       </c>
       <c r="E30">
-        <v>-260.0119999999999</v>
+        <v>-234.8409999999999</v>
       </c>
       <c r="F30">
-        <v>704.788</v>
+        <v>729.9590000000001</v>
       </c>
       <c r="G30">
         <v>105.7</v>
@@ -3741,28 +3741,28 @@
         <v>253.886</v>
       </c>
       <c r="M30">
-        <v>38.2699884</v>
+        <v>39.63677370000001</v>
       </c>
       <c r="N30">
-        <v>215.6160116</v>
+        <v>214.2492263</v>
       </c>
       <c r="O30">
-        <v>32.34240173999999</v>
+        <v>32.137383945</v>
       </c>
       <c r="P30">
-        <v>183.27360986</v>
+        <v>182.111842355</v>
       </c>
       <c r="Q30">
-        <v>183.76260986</v>
+        <v>182.600842355</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1035935345725894</v>
+        <v>0.1043157625767457</v>
       </c>
       <c r="T30">
-        <v>0.7532434968312817</v>
+        <v>0.7626565488514321</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.634075697812335</v>
+        <v>6.405314466853288</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08744914142948945</v>
+        <v>0.0873875379667145</v>
       </c>
       <c r="C31">
-        <v>2287.585947718334</v>
+        <v>2266.728252631617</v>
       </c>
       <c r="D31">
-        <v>2911.844947718334</v>
+        <v>2916.158252631617</v>
       </c>
       <c r="E31">
-        <v>-234.841</v>
+        <v>-209.67</v>
       </c>
       <c r="F31">
-        <v>729.9589999999999</v>
+        <v>755.13</v>
       </c>
       <c r="G31">
         <v>105.7</v>
@@ -3823,28 +3823,28 @@
         <v>253.886</v>
       </c>
       <c r="M31">
-        <v>39.6367737</v>
+        <v>41.003559</v>
       </c>
       <c r="N31">
-        <v>214.2492263</v>
+        <v>212.882441</v>
       </c>
       <c r="O31">
-        <v>32.137383945</v>
+        <v>31.93236615</v>
       </c>
       <c r="P31">
-        <v>182.111842355</v>
+        <v>180.95007485</v>
       </c>
       <c r="Q31">
-        <v>182.600842355</v>
+        <v>181.43907485</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1043157625767457</v>
+        <v>0.105058625666735</v>
       </c>
       <c r="T31">
-        <v>0.7626565488514321</v>
+        <v>0.7723385452150153</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.40531446685329</v>
+        <v>6.191803984624847</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0873875379667145</v>
+        <v>0.08758943450393955</v>
       </c>
       <c r="C32">
-        <v>2266.728252631617</v>
+        <v>2227.468470139213</v>
       </c>
       <c r="D32">
-        <v>2916.158252631617</v>
+        <v>2902.069470139213</v>
       </c>
       <c r="E32">
-        <v>-209.67</v>
+        <v>-184.499</v>
       </c>
       <c r="F32">
-        <v>755.13</v>
+        <v>780.3009999999999</v>
       </c>
       <c r="G32">
         <v>105.7</v>
@@ -3905,45 +3905,45 @@
         <v>253.886</v>
       </c>
       <c r="M32">
-        <v>41.003559</v>
+        <v>43.1506453</v>
       </c>
       <c r="N32">
-        <v>212.882441</v>
+        <v>210.7353547</v>
       </c>
       <c r="O32">
-        <v>31.93236615</v>
+        <v>31.610303205</v>
       </c>
       <c r="P32">
-        <v>180.95007485</v>
+        <v>179.125051495</v>
       </c>
       <c r="Q32">
-        <v>181.43907485</v>
+        <v>179.614051495</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.105058625666735</v>
+        <v>0.1058230210202023</v>
       </c>
       <c r="T32">
-        <v>0.7723385452150153</v>
+        <v>0.7823011791543546</v>
       </c>
       <c r="U32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.15</v>
       </c>
       <c r="W32">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.191803984624847</v>
+        <v>5.883712705450548</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08758943450393955</v>
+        <v>0.08753633104116461</v>
       </c>
       <c r="C33">
-        <v>2227.468470139213</v>
+        <v>2205.989935054871</v>
       </c>
       <c r="D33">
-        <v>2902.069470139213</v>
+        <v>2905.761935054872</v>
       </c>
       <c r="E33">
-        <v>-184.499</v>
+        <v>-159.328</v>
       </c>
       <c r="F33">
-        <v>780.3009999999999</v>
+        <v>805.472</v>
       </c>
       <c r="G33">
         <v>105.7</v>
@@ -3987,28 +3987,28 @@
         <v>253.886</v>
       </c>
       <c r="M33">
-        <v>43.1506453</v>
+        <v>44.5426016</v>
       </c>
       <c r="N33">
-        <v>210.7353547</v>
+        <v>209.3433984</v>
       </c>
       <c r="O33">
-        <v>31.610303205</v>
+        <v>31.40150976</v>
       </c>
       <c r="P33">
-        <v>179.125051495</v>
+        <v>177.94188864</v>
       </c>
       <c r="Q33">
-        <v>179.614051495</v>
+        <v>178.43088864</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1058230210202023</v>
+        <v>0.106609898589948</v>
       </c>
       <c r="T33">
-        <v>0.7823011791543546</v>
+        <v>0.7925568317389685</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.883712705450548</v>
+        <v>5.699846683405219</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08753633104116461</v>
+        <v>0.08748322757838967</v>
       </c>
       <c r="C34">
-        <v>2205.989935054871</v>
+        <v>2184.520808199431</v>
       </c>
       <c r="D34">
-        <v>2905.761935054872</v>
+        <v>2909.463808199432</v>
       </c>
       <c r="E34">
-        <v>-159.328</v>
+        <v>-134.1569999999999</v>
       </c>
       <c r="F34">
-        <v>805.472</v>
+        <v>830.643</v>
       </c>
       <c r="G34">
         <v>105.7</v>
@@ -4069,28 +4069,28 @@
         <v>253.886</v>
       </c>
       <c r="M34">
-        <v>44.5426016</v>
+        <v>45.9345579</v>
       </c>
       <c r="N34">
-        <v>209.3433984</v>
+        <v>207.9514421</v>
       </c>
       <c r="O34">
-        <v>31.40150976</v>
+        <v>31.192716315</v>
       </c>
       <c r="P34">
-        <v>177.94188864</v>
+        <v>176.758725785</v>
       </c>
       <c r="Q34">
-        <v>178.43088864</v>
+        <v>177.247725785</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.106609898589948</v>
+        <v>0.1074202650423726</v>
       </c>
       <c r="T34">
-        <v>0.7925568317389685</v>
+        <v>0.8031186232067054</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.699846683405219</v>
+        <v>5.527124056635364</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08748322757838967</v>
+        <v>0.08743012411561471</v>
       </c>
       <c r="C35">
-        <v>2184.520808199431</v>
+        <v>2163.061125576356</v>
       </c>
       <c r="D35">
-        <v>2909.463808199432</v>
+        <v>2913.175125576357</v>
       </c>
       <c r="E35">
-        <v>-134.1569999999999</v>
+        <v>-108.9859999999999</v>
       </c>
       <c r="F35">
-        <v>830.643</v>
+        <v>855.8140000000001</v>
       </c>
       <c r="G35">
         <v>105.7</v>
@@ -4151,28 +4151,28 @@
         <v>253.886</v>
       </c>
       <c r="M35">
-        <v>45.9345579</v>
+        <v>47.32651420000001</v>
       </c>
       <c r="N35">
-        <v>207.9514421</v>
+        <v>206.5594858</v>
       </c>
       <c r="O35">
-        <v>31.192716315</v>
+        <v>30.98392287</v>
       </c>
       <c r="P35">
-        <v>176.758725785</v>
+        <v>175.57556293</v>
       </c>
       <c r="Q35">
-        <v>177.247725785</v>
+        <v>176.06456293</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1074202650423726</v>
+        <v>0.1082551880539617</v>
       </c>
       <c r="T35">
-        <v>0.8031186232067054</v>
+        <v>0.8140004689613433</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.527124056635364</v>
+        <v>5.364561584381383</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08743012411561471</v>
+        <v>0.08737702065283978</v>
       </c>
       <c r="C36">
-        <v>2163.061125576356</v>
+        <v>2141.610923373043</v>
       </c>
       <c r="D36">
-        <v>2913.175125576357</v>
+        <v>2916.895923373043</v>
       </c>
       <c r="E36">
-        <v>-108.9859999999999</v>
+        <v>-83.81499999999994</v>
       </c>
       <c r="F36">
-        <v>855.8140000000001</v>
+        <v>880.985</v>
       </c>
       <c r="G36">
         <v>105.7</v>
@@ -4233,28 +4233,28 @@
         <v>253.886</v>
       </c>
       <c r="M36">
-        <v>47.32651420000001</v>
+        <v>48.7184705</v>
       </c>
       <c r="N36">
-        <v>206.5594858</v>
+        <v>205.1675295</v>
       </c>
       <c r="O36">
-        <v>30.98392287</v>
+        <v>30.775129425</v>
       </c>
       <c r="P36">
-        <v>175.57556293</v>
+        <v>174.392400075</v>
       </c>
       <c r="Q36">
-        <v>176.06456293</v>
+        <v>174.881400075</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1082551880539617</v>
+        <v>0.1091158010043689</v>
       </c>
       <c r="T36">
-        <v>0.8140004689613433</v>
+        <v>0.8252171407392008</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.364561584381383</v>
+        <v>5.2112883962562</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08737702065283978</v>
+        <v>0.08732391719006483</v>
       </c>
       <c r="C37">
-        <v>2141.610923373043</v>
+        <v>2120.170237962013</v>
       </c>
       <c r="D37">
-        <v>2916.895923373043</v>
+        <v>2920.626237962013</v>
       </c>
       <c r="E37">
-        <v>-83.81499999999994</v>
+        <v>-58.64399999999989</v>
       </c>
       <c r="F37">
-        <v>880.985</v>
+        <v>906.1560000000001</v>
       </c>
       <c r="G37">
         <v>105.7</v>
@@ -4315,28 +4315,28 @@
         <v>253.886</v>
       </c>
       <c r="M37">
-        <v>48.7184705</v>
+        <v>50.11042680000001</v>
       </c>
       <c r="N37">
-        <v>205.1675295</v>
+        <v>203.7755732</v>
       </c>
       <c r="O37">
-        <v>30.775129425</v>
+        <v>30.56633598</v>
       </c>
       <c r="P37">
-        <v>174.392400075</v>
+        <v>173.20923722</v>
       </c>
       <c r="Q37">
-        <v>174.881400075</v>
+        <v>173.69823722</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1091158010043689</v>
+        <v>0.1100033081094763</v>
       </c>
       <c r="T37">
-        <v>0.8252171407392008</v>
+        <v>0.8367843335101164</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.2112883962562</v>
+        <v>5.066530385249083</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08732391719006484</v>
+        <v>0.0872708137272899</v>
       </c>
       <c r="C38">
-        <v>2120.170237962011</v>
+        <v>2098.739105902077</v>
       </c>
       <c r="D38">
-        <v>2920.626237962012</v>
+        <v>2924.366105902078</v>
       </c>
       <c r="E38">
-        <v>-58.64400000000001</v>
+        <v>-33.47299999999996</v>
       </c>
       <c r="F38">
-        <v>906.1559999999999</v>
+        <v>931.327</v>
       </c>
       <c r="G38">
         <v>105.7</v>
@@ -4397,28 +4397,28 @@
         <v>253.886</v>
       </c>
       <c r="M38">
-        <v>50.1104268</v>
+        <v>51.5023831</v>
       </c>
       <c r="N38">
-        <v>203.7755732</v>
+        <v>202.3836169</v>
       </c>
       <c r="O38">
-        <v>30.56633598</v>
+        <v>30.357542535</v>
       </c>
       <c r="P38">
-        <v>173.20923722</v>
+        <v>172.026074365</v>
       </c>
       <c r="Q38">
-        <v>173.69823722</v>
+        <v>172.515074365</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1100033081094763</v>
+        <v>0.1109189900433173</v>
       </c>
       <c r="T38">
-        <v>0.8367843335101163</v>
+        <v>0.8487187387499499</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.066530385249084</v>
+        <v>4.929597131593702</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0872708137272899</v>
+        <v>0.08721771026451494</v>
       </c>
       <c r="C39">
-        <v>2098.739105902077</v>
+        <v>2077.317563939553</v>
       </c>
       <c r="D39">
-        <v>2924.366105902078</v>
+        <v>2928.115563939553</v>
       </c>
       <c r="E39">
-        <v>-33.47299999999996</v>
+        <v>-8.302000000000021</v>
       </c>
       <c r="F39">
-        <v>931.327</v>
+        <v>956.4979999999999</v>
       </c>
       <c r="G39">
         <v>105.7</v>
@@ -4479,28 +4479,28 @@
         <v>253.886</v>
       </c>
       <c r="M39">
-        <v>51.5023831</v>
+        <v>52.8943394</v>
       </c>
       <c r="N39">
-        <v>202.3836169</v>
+        <v>200.9916606</v>
       </c>
       <c r="O39">
-        <v>30.357542535</v>
+        <v>30.14874909</v>
       </c>
       <c r="P39">
-        <v>172.026074365</v>
+        <v>170.84291151</v>
       </c>
       <c r="Q39">
-        <v>172.515074365</v>
+        <v>171.33191151</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1109189900433173</v>
+        <v>0.1118642101040564</v>
       </c>
       <c r="T39">
-        <v>0.8487187387499499</v>
+        <v>0.8610381248039716</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.929597131593702</v>
+        <v>4.799870891288606</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08721771026451494</v>
+        <v>0.08716460680174</v>
       </c>
       <c r="C40">
-        <v>2077.317563939553</v>
+        <v>2055.905649009445</v>
       </c>
       <c r="D40">
-        <v>2928.115563939553</v>
+        <v>2931.874649009445</v>
       </c>
       <c r="E40">
-        <v>-8.302000000000021</v>
+        <v>16.86900000000003</v>
       </c>
       <c r="F40">
-        <v>956.4979999999999</v>
+        <v>981.669</v>
       </c>
       <c r="G40">
         <v>105.7</v>
@@ -4561,28 +4561,28 @@
         <v>253.886</v>
       </c>
       <c r="M40">
-        <v>52.8943394</v>
+        <v>54.2862957</v>
       </c>
       <c r="N40">
-        <v>200.9916606</v>
+        <v>199.5997043</v>
       </c>
       <c r="O40">
-        <v>30.14874909</v>
+        <v>29.939955645</v>
       </c>
       <c r="P40">
-        <v>170.84291151</v>
+        <v>169.659748655</v>
       </c>
       <c r="Q40">
-        <v>171.33191151</v>
+        <v>170.148748655</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1118642101040564</v>
+        <v>0.112840420986459</v>
       </c>
       <c r="T40">
-        <v>0.8610381248039716</v>
+        <v>0.8737614251548464</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.799870891288606</v>
+        <v>4.676797278691462</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08716460680174</v>
+        <v>0.08711150333896507</v>
       </c>
       <c r="C41">
-        <v>2055.905649009445</v>
+        <v>2034.503398236675</v>
       </c>
       <c r="D41">
-        <v>2931.874649009445</v>
+        <v>2935.643398236676</v>
       </c>
       <c r="E41">
-        <v>16.86900000000003</v>
+        <v>42.04000000000008</v>
       </c>
       <c r="F41">
-        <v>981.669</v>
+        <v>1006.84</v>
       </c>
       <c r="G41">
         <v>105.7</v>
@@ -4643,28 +4643,28 @@
         <v>253.886</v>
       </c>
       <c r="M41">
-        <v>54.2862957</v>
+        <v>55.678252</v>
       </c>
       <c r="N41">
-        <v>199.5997043</v>
+        <v>198.207748</v>
       </c>
       <c r="O41">
-        <v>29.939955645</v>
+        <v>29.7311622</v>
       </c>
       <c r="P41">
-        <v>169.659748655</v>
+        <v>168.4765858</v>
       </c>
       <c r="Q41">
-        <v>170.148748655</v>
+        <v>168.9655858</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.112840420986459</v>
+        <v>0.1138491722316085</v>
       </c>
       <c r="T41">
-        <v>0.8737614251548464</v>
+        <v>0.8869088355174173</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.676797278691462</v>
+        <v>4.559877346724175</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08711150333896507</v>
+        <v>0.08792964987619012</v>
       </c>
       <c r="C42">
-        <v>2034.503398236675</v>
+        <v>1952.322988287786</v>
       </c>
       <c r="D42">
-        <v>2935.643398236676</v>
+        <v>2878.633988287786</v>
       </c>
       <c r="E42">
-        <v>42.04000000000008</v>
+        <v>67.21100000000001</v>
       </c>
       <c r="F42">
-        <v>1006.84</v>
+        <v>1032.011</v>
       </c>
       <c r="G42">
         <v>105.7</v>
@@ -4725,45 +4725,45 @@
         <v>253.886</v>
       </c>
       <c r="M42">
-        <v>55.678252</v>
+        <v>59.6502358</v>
       </c>
       <c r="N42">
-        <v>198.207748</v>
+        <v>194.2357642</v>
       </c>
       <c r="O42">
-        <v>29.7311622</v>
+        <v>29.13536463</v>
       </c>
       <c r="P42">
-        <v>168.4765858</v>
+        <v>165.10039957</v>
       </c>
       <c r="Q42">
-        <v>168.9655858</v>
+        <v>165.58939957</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1138491722316085</v>
+        <v>0.1148921184342205</v>
       </c>
       <c r="T42">
-        <v>0.8869088355174173</v>
+        <v>0.9005019208075327</v>
       </c>
       <c r="U42">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V42">
         <v>0.15</v>
       </c>
       <c r="W42">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.559877346724175</v>
+        <v>4.256244700377194</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08792964987619012</v>
+        <v>0.08789779641341516</v>
       </c>
       <c r="C43">
-        <v>1952.322988287786</v>
+        <v>1929.330117985791</v>
       </c>
       <c r="D43">
-        <v>2878.633988287786</v>
+        <v>2880.812117985791</v>
       </c>
       <c r="E43">
-        <v>67.21100000000001</v>
+        <v>92.38200000000006</v>
       </c>
       <c r="F43">
-        <v>1032.011</v>
+        <v>1057.182</v>
       </c>
       <c r="G43">
         <v>105.7</v>
@@ -4807,28 +4807,28 @@
         <v>253.886</v>
       </c>
       <c r="M43">
-        <v>59.6502358</v>
+        <v>61.1051196</v>
       </c>
       <c r="N43">
-        <v>194.2357642</v>
+        <v>192.7808804</v>
       </c>
       <c r="O43">
-        <v>29.13536463</v>
+        <v>28.91713206</v>
       </c>
       <c r="P43">
-        <v>165.10039957</v>
+        <v>163.86374834</v>
       </c>
       <c r="Q43">
-        <v>165.58939957</v>
+        <v>164.35274834</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1148921184342205</v>
+        <v>0.1159710282989917</v>
       </c>
       <c r="T43">
-        <v>0.9005019208075327</v>
+        <v>0.9145637331766177</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.256244700377194</v>
+        <v>4.154905540844404</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08789779641341518</v>
+        <v>0.08786594295064024</v>
       </c>
       <c r="C44">
-        <v>1929.33011798579</v>
+        <v>1906.34054636051</v>
       </c>
       <c r="D44">
-        <v>2880.81211798579</v>
+        <v>2882.99354636051</v>
       </c>
       <c r="E44">
-        <v>92.38200000000006</v>
+        <v>117.5529999999999</v>
       </c>
       <c r="F44">
-        <v>1057.182</v>
+        <v>1082.353</v>
       </c>
       <c r="G44">
         <v>105.7</v>
@@ -4889,28 +4889,28 @@
         <v>253.886</v>
       </c>
       <c r="M44">
-        <v>61.1051196</v>
+        <v>62.56000339999999</v>
       </c>
       <c r="N44">
-        <v>192.7808804</v>
+        <v>191.3259966</v>
       </c>
       <c r="O44">
-        <v>28.91713206</v>
+        <v>28.69889949</v>
       </c>
       <c r="P44">
-        <v>163.86374834</v>
+        <v>162.62709711</v>
       </c>
       <c r="Q44">
-        <v>164.35274834</v>
+        <v>163.11609711</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1159710282989917</v>
+        <v>0.117087794650246</v>
       </c>
       <c r="T44">
-        <v>0.9145637331766175</v>
+        <v>0.9291189424709336</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.154905540844404</v>
+        <v>4.058279830592209</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08786594295064024</v>
+        <v>0.08914308948786528</v>
       </c>
       <c r="C45">
-        <v>1906.34054636051</v>
+        <v>1796.219320890142</v>
       </c>
       <c r="D45">
-        <v>2882.99354636051</v>
+        <v>2798.043320890142</v>
       </c>
       <c r="E45">
-        <v>117.5529999999999</v>
+        <v>142.7239999999999</v>
       </c>
       <c r="F45">
-        <v>1082.353</v>
+        <v>1107.524</v>
       </c>
       <c r="G45">
         <v>105.7</v>
@@ -4971,45 +4971,45 @@
         <v>253.886</v>
       </c>
       <c r="M45">
-        <v>62.56000339999999</v>
+        <v>67.89122119999999</v>
       </c>
       <c r="N45">
-        <v>191.3259966</v>
+        <v>185.9947788</v>
       </c>
       <c r="O45">
-        <v>28.69889949</v>
+        <v>27.89921682</v>
       </c>
       <c r="P45">
-        <v>162.62709711</v>
+        <v>158.09556198</v>
       </c>
       <c r="Q45">
-        <v>163.11609711</v>
+        <v>158.58456198</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.117087794650246</v>
+        <v>0.1182444455140451</v>
       </c>
       <c r="T45">
-        <v>0.9291189424709336</v>
+        <v>0.944193980668618</v>
       </c>
       <c r="U45">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V45">
         <v>0.15</v>
       </c>
       <c r="W45">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.058279830592209</v>
+        <v>3.739599840929066</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08914308948786528</v>
+        <v>0.08914098602509034</v>
       </c>
       <c r="C46">
-        <v>1796.219320890142</v>
+        <v>1771.184117984485</v>
       </c>
       <c r="D46">
-        <v>2798.043320890142</v>
+        <v>2798.179117984485</v>
       </c>
       <c r="E46">
-        <v>142.7239999999999</v>
+        <v>167.895</v>
       </c>
       <c r="F46">
-        <v>1107.524</v>
+        <v>1132.695</v>
       </c>
       <c r="G46">
         <v>105.7</v>
@@ -5053,28 +5053,28 @@
         <v>253.886</v>
       </c>
       <c r="M46">
-        <v>67.89122119999999</v>
+        <v>69.4342035</v>
       </c>
       <c r="N46">
-        <v>185.9947788</v>
+        <v>184.4517965</v>
       </c>
       <c r="O46">
-        <v>27.89921682</v>
+        <v>27.667769475</v>
       </c>
       <c r="P46">
-        <v>158.09556198</v>
+        <v>156.784027025</v>
       </c>
       <c r="Q46">
-        <v>158.58456198</v>
+        <v>157.273027025</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1182444455140451</v>
+        <v>0.1194431564092552</v>
       </c>
       <c r="T46">
-        <v>0.944193980668618</v>
+        <v>0.9598172020734911</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.739599840929066</v>
+        <v>3.656497622241753</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08914098602509034</v>
+        <v>0.08913888256231541</v>
       </c>
       <c r="C47">
-        <v>1771.184117984485</v>
+        <v>1746.148928260715</v>
       </c>
       <c r="D47">
-        <v>2798.179117984485</v>
+        <v>2798.314928260715</v>
       </c>
       <c r="E47">
-        <v>167.895</v>
+        <v>193.066</v>
       </c>
       <c r="F47">
-        <v>1132.695</v>
+        <v>1157.866</v>
       </c>
       <c r="G47">
         <v>105.7</v>
@@ -5135,28 +5135,28 @@
         <v>253.886</v>
       </c>
       <c r="M47">
-        <v>69.4342035</v>
+        <v>70.9771858</v>
       </c>
       <c r="N47">
-        <v>184.4517965</v>
+        <v>182.9088142</v>
       </c>
       <c r="O47">
-        <v>27.667769475</v>
+        <v>27.43632213</v>
       </c>
       <c r="P47">
-        <v>156.784027025</v>
+        <v>155.47249207</v>
       </c>
       <c r="Q47">
-        <v>157.273027025</v>
+        <v>155.96149207</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1194431564092552</v>
+        <v>0.1206862640042878</v>
       </c>
       <c r="T47">
-        <v>0.9598172020734911</v>
+        <v>0.9760190613081743</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.656497622241753</v>
+        <v>3.577008543497367</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08913888256231541</v>
+        <v>0.08913677909954046</v>
       </c>
       <c r="C48">
-        <v>1746.148928260715</v>
+        <v>1721.113751720752</v>
       </c>
       <c r="D48">
-        <v>2798.314928260715</v>
+        <v>2798.450751720753</v>
       </c>
       <c r="E48">
-        <v>193.066</v>
+        <v>218.2370000000001</v>
       </c>
       <c r="F48">
-        <v>1157.866</v>
+        <v>1183.037</v>
       </c>
       <c r="G48">
         <v>105.7</v>
@@ -5217,28 +5217,28 @@
         <v>253.886</v>
       </c>
       <c r="M48">
-        <v>70.9771858</v>
+        <v>72.52016810000001</v>
       </c>
       <c r="N48">
-        <v>182.9088142</v>
+        <v>181.3658319</v>
       </c>
       <c r="O48">
-        <v>27.43632213</v>
+        <v>27.204874785</v>
       </c>
       <c r="P48">
-        <v>155.47249207</v>
+        <v>154.160957115</v>
       </c>
       <c r="Q48">
-        <v>155.96149207</v>
+        <v>154.649957115</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1206862640042878</v>
+        <v>0.1219762813198876</v>
       </c>
       <c r="T48">
-        <v>0.9760190613081743</v>
+        <v>0.9928323114573737</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.577008543497367</v>
+        <v>3.500901978742104</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08913677909954046</v>
+        <v>0.09027707563676551</v>
       </c>
       <c r="C49">
-        <v>1721.113751720752</v>
+        <v>1624.196494663684</v>
       </c>
       <c r="D49">
-        <v>2798.450751720753</v>
+        <v>2726.704494663684</v>
       </c>
       <c r="E49">
-        <v>218.2370000000001</v>
+        <v>243.4080000000001</v>
       </c>
       <c r="F49">
-        <v>1183.037</v>
+        <v>1208.208</v>
       </c>
       <c r="G49">
         <v>105.7</v>
@@ -5299,45 +5299,45 @@
         <v>253.886</v>
       </c>
       <c r="M49">
-        <v>72.52016810000001</v>
+        <v>77.44613280000002</v>
       </c>
       <c r="N49">
-        <v>181.3658319</v>
+        <v>176.4398672</v>
       </c>
       <c r="O49">
-        <v>27.204874785</v>
+        <v>26.46598008</v>
       </c>
       <c r="P49">
-        <v>154.160957115</v>
+        <v>149.97388712</v>
       </c>
       <c r="Q49">
-        <v>154.649957115</v>
+        <v>150.46288712</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1219762813198876</v>
+        <v>0.1233159146860875</v>
       </c>
       <c r="T49">
-        <v>0.9928323114573737</v>
+        <v>1.01029222507385</v>
       </c>
       <c r="U49">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V49">
         <v>0.15</v>
       </c>
       <c r="W49">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.500901978742104</v>
+        <v>3.278226953638154</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09027707563676551</v>
+        <v>0.09029877217399056</v>
       </c>
       <c r="C50">
-        <v>1624.196494663684</v>
+        <v>1597.696018755027</v>
       </c>
       <c r="D50">
-        <v>2726.704494663684</v>
+        <v>2725.375018755027</v>
       </c>
       <c r="E50">
-        <v>243.4079999999999</v>
+        <v>268.579</v>
       </c>
       <c r="F50">
-        <v>1208.208</v>
+        <v>1233.379</v>
       </c>
       <c r="G50">
         <v>105.7</v>
@@ -5381,28 +5381,28 @@
         <v>253.886</v>
       </c>
       <c r="M50">
-        <v>77.4461328</v>
+        <v>79.0595939</v>
       </c>
       <c r="N50">
-        <v>176.4398672</v>
+        <v>174.8264061</v>
       </c>
       <c r="O50">
-        <v>26.46598008</v>
+        <v>26.223960915</v>
       </c>
       <c r="P50">
-        <v>149.97388712</v>
+        <v>148.602445185</v>
       </c>
       <c r="Q50">
-        <v>150.46288712</v>
+        <v>149.091445185</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1233159146860875</v>
+        <v>0.1247080826940991</v>
       </c>
       <c r="T50">
-        <v>1.01029222507385</v>
+        <v>1.02843684118509</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.278226953638155</v>
+        <v>3.21132436274758</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09029877217399056</v>
+        <v>0.09032046871121562</v>
       </c>
       <c r="C51">
-        <v>1597.696018755027</v>
+        <v>1571.196838655886</v>
       </c>
       <c r="D51">
-        <v>2725.375018755027</v>
+        <v>2724.046838655886</v>
       </c>
       <c r="E51">
-        <v>268.579</v>
+        <v>293.75</v>
       </c>
       <c r="F51">
-        <v>1233.379</v>
+        <v>1258.55</v>
       </c>
       <c r="G51">
         <v>105.7</v>
@@ -5463,28 +5463,28 @@
         <v>253.886</v>
       </c>
       <c r="M51">
-        <v>79.0595939</v>
+        <v>80.67305500000001</v>
       </c>
       <c r="N51">
-        <v>174.8264061</v>
+        <v>173.212945</v>
       </c>
       <c r="O51">
-        <v>26.223960915</v>
+        <v>25.98194175</v>
       </c>
       <c r="P51">
-        <v>148.602445185</v>
+        <v>147.23100325</v>
       </c>
       <c r="Q51">
-        <v>149.091445185</v>
+        <v>147.72000325</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1247080826940991</v>
+        <v>0.1261559374224312</v>
       </c>
       <c r="T51">
-        <v>1.02843684118509</v>
+        <v>1.04730724194078</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.21132436274758</v>
+        <v>3.147097875492629</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09032046871121562</v>
+        <v>0.09034216524844067</v>
       </c>
       <c r="C52">
-        <v>1571.196838655886</v>
+        <v>1544.698952472692</v>
       </c>
       <c r="D52">
-        <v>2724.046838655886</v>
+        <v>2722.719952472692</v>
       </c>
       <c r="E52">
-        <v>293.75</v>
+        <v>318.921</v>
       </c>
       <c r="F52">
-        <v>1258.55</v>
+        <v>1283.721</v>
       </c>
       <c r="G52">
         <v>105.7</v>
@@ -5545,28 +5545,28 @@
         <v>253.886</v>
       </c>
       <c r="M52">
-        <v>80.67305500000001</v>
+        <v>82.2865161</v>
       </c>
       <c r="N52">
-        <v>173.212945</v>
+        <v>171.5994839</v>
       </c>
       <c r="O52">
-        <v>25.98194175</v>
+        <v>25.739922585</v>
       </c>
       <c r="P52">
-        <v>147.23100325</v>
+        <v>145.859561315</v>
       </c>
       <c r="Q52">
-        <v>147.72000325</v>
+        <v>146.348561315</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1261559374224312</v>
+        <v>0.1276628882621238</v>
       </c>
       <c r="T52">
-        <v>1.04730724194078</v>
+        <v>1.066947863135477</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.147097875492629</v>
+        <v>3.085390074012381</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09034216524844067</v>
+        <v>0.09036386178566573</v>
       </c>
       <c r="C53">
-        <v>1544.698952472692</v>
+        <v>1518.202358315562</v>
       </c>
       <c r="D53">
-        <v>2722.719952472692</v>
+        <v>2721.394358315562</v>
       </c>
       <c r="E53">
-        <v>318.921</v>
+        <v>344.0920000000001</v>
       </c>
       <c r="F53">
-        <v>1283.721</v>
+        <v>1308.892</v>
       </c>
       <c r="G53">
         <v>105.7</v>
@@ -5627,28 +5627,28 @@
         <v>253.886</v>
       </c>
       <c r="M53">
-        <v>82.2865161</v>
+        <v>83.89997720000001</v>
       </c>
       <c r="N53">
-        <v>171.5994839</v>
+        <v>169.9860228</v>
       </c>
       <c r="O53">
-        <v>25.739922585</v>
+        <v>25.49790342</v>
       </c>
       <c r="P53">
-        <v>145.859561315</v>
+        <v>144.48811938</v>
       </c>
       <c r="Q53">
-        <v>146.348561315</v>
+        <v>144.97711938</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1276628882621238</v>
+        <v>0.1292326287201369</v>
       </c>
       <c r="T53">
-        <v>1.066947863135477</v>
+        <v>1.087406843546621</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.085390074012381</v>
+        <v>3.026055649512143</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09036386178566573</v>
+        <v>0.09389945832289079</v>
       </c>
       <c r="C54">
-        <v>1518.202358315562</v>
+        <v>1292.99267170305</v>
       </c>
       <c r="D54">
-        <v>2721.394358315562</v>
+        <v>2521.35567170305</v>
       </c>
       <c r="E54">
-        <v>344.0920000000001</v>
+        <v>369.2630000000001</v>
       </c>
       <c r="F54">
-        <v>1308.892</v>
+        <v>1334.063</v>
       </c>
       <c r="G54">
         <v>105.7</v>
@@ -5709,45 +5709,45 @@
         <v>253.886</v>
       </c>
       <c r="M54">
-        <v>83.89997720000001</v>
+        <v>95.91912970000001</v>
       </c>
       <c r="N54">
-        <v>169.9860228</v>
+        <v>157.9668703</v>
       </c>
       <c r="O54">
-        <v>25.49790342</v>
+        <v>23.695030545</v>
       </c>
       <c r="P54">
-        <v>144.48811938</v>
+        <v>134.271839755</v>
       </c>
       <c r="Q54">
-        <v>144.97711938</v>
+        <v>134.760839755</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1292326287201369</v>
+        <v>0.1308691666444485</v>
       </c>
       <c r="T54">
-        <v>1.087406843546621</v>
+        <v>1.108736418868876</v>
       </c>
       <c r="U54">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V54">
         <v>0.15</v>
       </c>
       <c r="W54">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.026055649512143</v>
+        <v>2.64687555854669</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09389945832289079</v>
+        <v>0.09398745486011584</v>
       </c>
       <c r="C55">
-        <v>1292.99267170305</v>
+        <v>1263.21734950204</v>
       </c>
       <c r="D55">
-        <v>2521.35567170305</v>
+        <v>2516.75134950204</v>
       </c>
       <c r="E55">
-        <v>369.2630000000001</v>
+        <v>394.4340000000002</v>
       </c>
       <c r="F55">
-        <v>1334.063</v>
+        <v>1359.234</v>
       </c>
       <c r="G55">
         <v>105.7</v>
@@ -5791,28 +5791,28 @@
         <v>253.886</v>
       </c>
       <c r="M55">
-        <v>95.91912970000001</v>
+        <v>97.72892460000001</v>
       </c>
       <c r="N55">
-        <v>157.9668703</v>
+        <v>156.1570754</v>
       </c>
       <c r="O55">
-        <v>23.695030545</v>
+        <v>23.42356131</v>
       </c>
       <c r="P55">
-        <v>134.271839755</v>
+        <v>132.73351409</v>
       </c>
       <c r="Q55">
-        <v>134.760839755</v>
+        <v>133.22251409</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1308691666444485</v>
+        <v>0.1325768583915562</v>
       </c>
       <c r="T55">
-        <v>1.108736418868876</v>
+        <v>1.13099336703123</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.64687555854669</v>
+        <v>2.59785934449953</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09398745486011584</v>
+        <v>0.09407545139734091</v>
       </c>
       <c r="C56">
-        <v>1263.21734950204</v>
+        <v>1233.458812826517</v>
       </c>
       <c r="D56">
-        <v>2516.75134950204</v>
+        <v>2512.163812826517</v>
       </c>
       <c r="E56">
-        <v>394.4340000000002</v>
+        <v>419.605</v>
       </c>
       <c r="F56">
-        <v>1359.234</v>
+        <v>1384.405</v>
       </c>
       <c r="G56">
         <v>105.7</v>
@@ -5873,28 +5873,28 @@
         <v>253.886</v>
       </c>
       <c r="M56">
-        <v>97.72892460000001</v>
+        <v>99.5387195</v>
       </c>
       <c r="N56">
-        <v>156.1570754</v>
+        <v>154.3472805</v>
       </c>
       <c r="O56">
-        <v>23.42356131</v>
+        <v>23.152092075</v>
       </c>
       <c r="P56">
-        <v>132.73351409</v>
+        <v>131.195188425</v>
       </c>
       <c r="Q56">
-        <v>133.22251409</v>
+        <v>131.684188425</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1325768583915562</v>
+        <v>0.1343604475496465</v>
       </c>
       <c r="T56">
-        <v>1.13099336703123</v>
+        <v>1.154239512889689</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.59785934449953</v>
+        <v>2.550625538235902</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09407545139734091</v>
+        <v>0.09416344793456596</v>
       </c>
       <c r="C57">
-        <v>1233.458812826517</v>
+        <v>1203.716970053481</v>
       </c>
       <c r="D57">
-        <v>2512.163812826517</v>
+        <v>2507.592970053482</v>
       </c>
       <c r="E57">
-        <v>419.605</v>
+        <v>444.7760000000001</v>
       </c>
       <c r="F57">
-        <v>1384.405</v>
+        <v>1409.576</v>
       </c>
       <c r="G57">
         <v>105.7</v>
@@ -5955,28 +5955,28 @@
         <v>253.886</v>
       </c>
       <c r="M57">
-        <v>99.5387195</v>
+        <v>101.3485144</v>
       </c>
       <c r="N57">
-        <v>154.3472805</v>
+        <v>152.5374856</v>
       </c>
       <c r="O57">
-        <v>23.152092075</v>
+        <v>22.88062283999999</v>
       </c>
       <c r="P57">
-        <v>131.195188425</v>
+        <v>129.65686276</v>
       </c>
       <c r="Q57">
-        <v>131.684188425</v>
+        <v>130.14586276</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1343604475496465</v>
+        <v>0.1362251089421954</v>
       </c>
       <c r="T57">
-        <v>1.154239512889689</v>
+        <v>1.178542301741713</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.550625538235902</v>
+        <v>2.505078653624547</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09416344793456596</v>
+        <v>0.096140994471791</v>
       </c>
       <c r="C58">
-        <v>1203.716970053481</v>
+        <v>1080.040133076466</v>
       </c>
       <c r="D58">
-        <v>2507.592970053482</v>
+        <v>2409.087133076466</v>
       </c>
       <c r="E58">
-        <v>444.7760000000001</v>
+        <v>469.9470000000001</v>
       </c>
       <c r="F58">
-        <v>1409.576</v>
+        <v>1434.747</v>
       </c>
       <c r="G58">
         <v>105.7</v>
@@ -6037,45 +6037,45 @@
         <v>253.886</v>
       </c>
       <c r="M58">
-        <v>101.3485144</v>
+        <v>108.7538226</v>
       </c>
       <c r="N58">
-        <v>152.5374856</v>
+        <v>145.1321774</v>
       </c>
       <c r="O58">
-        <v>22.88062283999999</v>
+        <v>21.76982661</v>
       </c>
       <c r="P58">
-        <v>129.65686276</v>
+        <v>123.36235079</v>
       </c>
       <c r="Q58">
-        <v>130.14586276</v>
+        <v>123.85135079</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1362251089421954</v>
+        <v>0.138176498771607</v>
       </c>
       <c r="T58">
-        <v>1.178542301741713</v>
+        <v>1.203975452865925</v>
       </c>
       <c r="U58">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V58">
         <v>0.15</v>
       </c>
       <c r="W58">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.505078653624547</v>
+        <v>2.334501849500966</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.096140994471791</v>
+        <v>0.09626214100901606</v>
       </c>
       <c r="C59">
-        <v>1080.040133076466</v>
+        <v>1049.085538520033</v>
       </c>
       <c r="D59">
-        <v>2409.087133076466</v>
+        <v>2403.303538520033</v>
       </c>
       <c r="E59">
-        <v>469.9470000000001</v>
+        <v>495.1180000000002</v>
       </c>
       <c r="F59">
-        <v>1434.747</v>
+        <v>1459.918</v>
       </c>
       <c r="G59">
         <v>105.7</v>
@@ -6119,28 +6119,28 @@
         <v>253.886</v>
       </c>
       <c r="M59">
-        <v>108.7538226</v>
+        <v>110.6617844</v>
       </c>
       <c r="N59">
-        <v>145.1321774</v>
+        <v>143.2242156</v>
       </c>
       <c r="O59">
-        <v>21.76982661</v>
+        <v>21.48363234</v>
       </c>
       <c r="P59">
-        <v>123.36235079</v>
+        <v>121.74058326</v>
       </c>
       <c r="Q59">
-        <v>123.85135079</v>
+        <v>122.22958326</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.138176498771607</v>
+        <v>0.1402208119262287</v>
       </c>
       <c r="T59">
-        <v>1.203975452865925</v>
+        <v>1.230619706424623</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.334501849500966</v>
+        <v>2.294251817613018</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09626214100901606</v>
+        <v>0.09638328754624112</v>
       </c>
       <c r="C60">
-        <v>1049.085538520033</v>
+        <v>1018.158647281721</v>
       </c>
       <c r="D60">
-        <v>2403.303538520033</v>
+        <v>2397.547647281721</v>
       </c>
       <c r="E60">
-        <v>495.1179999999999</v>
+        <v>520.289</v>
       </c>
       <c r="F60">
-        <v>1459.918</v>
+        <v>1485.089</v>
       </c>
       <c r="G60">
         <v>105.7</v>
@@ -6201,28 +6201,28 @@
         <v>253.886</v>
       </c>
       <c r="M60">
-        <v>110.6617844</v>
+        <v>112.5697462</v>
       </c>
       <c r="N60">
-        <v>143.2242156</v>
+        <v>141.3162538</v>
       </c>
       <c r="O60">
-        <v>21.48363234</v>
+        <v>21.19743806999999</v>
       </c>
       <c r="P60">
-        <v>121.74058326</v>
+        <v>120.11881573</v>
       </c>
       <c r="Q60">
-        <v>122.22958326</v>
+        <v>120.60781573</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1402208119262287</v>
+        <v>0.1423648476737588</v>
       </c>
       <c r="T60">
-        <v>1.230619706424623</v>
+        <v>1.258563679669111</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.294251817613018</v>
+        <v>2.255366193585679</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09638328754624112</v>
+        <v>0.09650443408346618</v>
       </c>
       <c r="C61">
-        <v>1018.158647281721</v>
+        <v>987.2592607894837</v>
       </c>
       <c r="D61">
-        <v>2397.547647281721</v>
+        <v>2391.819260789484</v>
       </c>
       <c r="E61">
-        <v>520.289</v>
+        <v>545.46</v>
       </c>
       <c r="F61">
-        <v>1485.089</v>
+        <v>1510.26</v>
       </c>
       <c r="G61">
         <v>105.7</v>
@@ -6283,28 +6283,28 @@
         <v>253.886</v>
       </c>
       <c r="M61">
-        <v>112.5697462</v>
+        <v>114.477708</v>
       </c>
       <c r="N61">
-        <v>141.3162538</v>
+        <v>139.408292</v>
       </c>
       <c r="O61">
-        <v>21.19743806999999</v>
+        <v>20.9112438</v>
       </c>
       <c r="P61">
-        <v>120.11881573</v>
+        <v>118.4970482</v>
       </c>
       <c r="Q61">
-        <v>120.60781573</v>
+        <v>118.9860482</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1423648476737588</v>
+        <v>0.1446160852086654</v>
       </c>
       <c r="T61">
-        <v>1.258563679669111</v>
+        <v>1.287904851575824</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.255366193585679</v>
+        <v>2.217776757025918</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09650443408346618</v>
+        <v>0.09662558062069124</v>
       </c>
       <c r="C62">
-        <v>987.2592607894837</v>
+        <v>956.3871823645206</v>
       </c>
       <c r="D62">
-        <v>2391.819260789484</v>
+        <v>2386.118182364521</v>
       </c>
       <c r="E62">
-        <v>545.46</v>
+        <v>570.6309999999999</v>
       </c>
       <c r="F62">
-        <v>1510.26</v>
+        <v>1535.431</v>
       </c>
       <c r="G62">
         <v>105.7</v>
@@ -6365,28 +6365,28 @@
         <v>253.886</v>
       </c>
       <c r="M62">
-        <v>114.477708</v>
+        <v>116.3856698</v>
       </c>
       <c r="N62">
-        <v>139.408292</v>
+        <v>137.5003302</v>
       </c>
       <c r="O62">
-        <v>20.9112438</v>
+        <v>20.62504953</v>
       </c>
       <c r="P62">
-        <v>118.4970482</v>
+        <v>116.87528067</v>
       </c>
       <c r="Q62">
-        <v>118.9860482</v>
+        <v>117.36428067</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1446160852086654</v>
+        <v>0.1469827708222852</v>
       </c>
       <c r="T62">
-        <v>1.287904851575824</v>
+        <v>1.318750698964932</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.217776757025918</v>
+        <v>2.1814197610091</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09662558062069124</v>
+        <v>0.0967467271579163</v>
       </c>
       <c r="C63">
-        <v>956.3871823645206</v>
+        <v>925.5422171987661</v>
       </c>
       <c r="D63">
-        <v>2386.118182364521</v>
+        <v>2380.444217198766</v>
       </c>
       <c r="E63">
-        <v>570.6309999999999</v>
+        <v>595.8019999999999</v>
       </c>
       <c r="F63">
-        <v>1535.431</v>
+        <v>1560.602</v>
       </c>
       <c r="G63">
         <v>105.7</v>
@@ -6447,28 +6447,28 @@
         <v>253.886</v>
       </c>
       <c r="M63">
-        <v>116.3856698</v>
+        <v>118.2936316</v>
       </c>
       <c r="N63">
-        <v>137.5003302</v>
+        <v>135.5923684</v>
       </c>
       <c r="O63">
-        <v>20.62504953</v>
+        <v>20.33885526</v>
       </c>
       <c r="P63">
-        <v>116.87528067</v>
+        <v>115.25351314</v>
       </c>
       <c r="Q63">
-        <v>117.36428067</v>
+        <v>115.74251314</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1469827708222852</v>
+        <v>0.1494740188366218</v>
       </c>
       <c r="T63">
-        <v>1.318750698964932</v>
+        <v>1.351220012006099</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.1814197610091</v>
+        <v>2.146235571315405</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.0967467271579163</v>
+        <v>0.09686787369514134</v>
       </c>
       <c r="C64">
-        <v>925.5422171987661</v>
+        <v>894.7241723327013</v>
       </c>
       <c r="D64">
-        <v>2380.444217198766</v>
+        <v>2374.797172332701</v>
       </c>
       <c r="E64">
-        <v>595.8019999999999</v>
+        <v>620.973</v>
       </c>
       <c r="F64">
-        <v>1560.602</v>
+        <v>1585.773</v>
       </c>
       <c r="G64">
         <v>105.7</v>
@@ -6529,28 +6529,28 @@
         <v>253.886</v>
       </c>
       <c r="M64">
-        <v>118.2936316</v>
+        <v>120.2015934</v>
       </c>
       <c r="N64">
-        <v>135.5923684</v>
+        <v>133.6844066</v>
       </c>
       <c r="O64">
-        <v>20.33885526</v>
+        <v>20.05266099</v>
       </c>
       <c r="P64">
-        <v>115.25351314</v>
+        <v>113.63174561</v>
       </c>
       <c r="Q64">
-        <v>115.74251314</v>
+        <v>114.12074561</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1494740188366218</v>
+        <v>0.1520999289057874</v>
       </c>
       <c r="T64">
-        <v>1.351220012006099</v>
+        <v>1.38544442304949</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.146235571315405</v>
+        <v>2.112168340024684</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09686787369514134</v>
+        <v>0.0969890202323664</v>
       </c>
       <c r="C65">
-        <v>894.7241723327013</v>
+        <v>863.9328566334752</v>
       </c>
       <c r="D65">
-        <v>2374.797172332701</v>
+        <v>2369.176856633475</v>
       </c>
       <c r="E65">
-        <v>620.973</v>
+        <v>646.144</v>
       </c>
       <c r="F65">
-        <v>1585.773</v>
+        <v>1610.944</v>
       </c>
       <c r="G65">
         <v>105.7</v>
@@ -6611,28 +6611,28 @@
         <v>253.886</v>
       </c>
       <c r="M65">
-        <v>120.2015934</v>
+        <v>122.1095552</v>
       </c>
       <c r="N65">
-        <v>133.6844066</v>
+        <v>131.7764448</v>
       </c>
       <c r="O65">
-        <v>20.05266099</v>
+        <v>19.76646672</v>
       </c>
       <c r="P65">
-        <v>113.63174561</v>
+        <v>112.00997808</v>
       </c>
       <c r="Q65">
-        <v>114.12074561</v>
+        <v>112.49897808</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1520999289057874</v>
+        <v>0.1548717228676844</v>
       </c>
       <c r="T65">
-        <v>1.38544442304949</v>
+        <v>1.42157019026196</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.112168340024684</v>
+        <v>2.079165709711798</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0969890202323664</v>
+        <v>0.09711016676959144</v>
       </c>
       <c r="C66">
-        <v>863.9328566334752</v>
+        <v>833.1680807733471</v>
       </c>
       <c r="D66">
-        <v>2369.176856633475</v>
+        <v>2363.583080773347</v>
       </c>
       <c r="E66">
-        <v>646.144</v>
+        <v>671.3150000000001</v>
       </c>
       <c r="F66">
-        <v>1610.944</v>
+        <v>1636.115</v>
       </c>
       <c r="G66">
         <v>105.7</v>
@@ -6693,28 +6693,28 @@
         <v>253.886</v>
       </c>
       <c r="M66">
-        <v>122.1095552</v>
+        <v>124.017517</v>
       </c>
       <c r="N66">
-        <v>131.7764448</v>
+        <v>129.868483</v>
       </c>
       <c r="O66">
-        <v>19.76646672</v>
+        <v>19.48027244999999</v>
       </c>
       <c r="P66">
-        <v>112.00997808</v>
+        <v>110.38821055</v>
       </c>
       <c r="Q66">
-        <v>112.49897808</v>
+        <v>110.87721055</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1548717228676844</v>
+        <v>0.1578019050559756</v>
       </c>
       <c r="T66">
-        <v>1.42157019026196</v>
+        <v>1.459760287029427</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.079165709711798</v>
+        <v>2.047178544947001</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09711016676959144</v>
+        <v>0.0972313133068165</v>
       </c>
       <c r="C67">
-        <v>833.1680807733471</v>
+        <v>802.4296572084218</v>
       </c>
       <c r="D67">
-        <v>2363.583080773347</v>
+        <v>2358.015657208422</v>
       </c>
       <c r="E67">
-        <v>671.3150000000001</v>
+        <v>696.4860000000001</v>
       </c>
       <c r="F67">
-        <v>1636.115</v>
+        <v>1661.286</v>
       </c>
       <c r="G67">
         <v>105.7</v>
@@ -6775,28 +6775,28 @@
         <v>253.886</v>
       </c>
       <c r="M67">
-        <v>124.017517</v>
+        <v>125.9254788</v>
       </c>
       <c r="N67">
-        <v>129.868483</v>
+        <v>127.9605212</v>
       </c>
       <c r="O67">
-        <v>19.48027244999999</v>
+        <v>19.19407817999999</v>
       </c>
       <c r="P67">
-        <v>110.38821055</v>
+        <v>108.76644302</v>
       </c>
       <c r="Q67">
-        <v>110.87721055</v>
+        <v>109.25544302</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1578019050559756</v>
+        <v>0.1609044509024015</v>
       </c>
       <c r="T67">
-        <v>1.459760287029427</v>
+        <v>1.500196860077333</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.047178544947001</v>
+        <v>2.01616068820538</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0972313133068165</v>
+        <v>0.1054393598440416</v>
       </c>
       <c r="C68">
-        <v>802.4296572084218</v>
+        <v>452.7296498467547</v>
       </c>
       <c r="D68">
-        <v>2358.015657208422</v>
+        <v>2033.486649846755</v>
       </c>
       <c r="E68">
-        <v>696.4860000000001</v>
+        <v>721.6570000000002</v>
       </c>
       <c r="F68">
-        <v>1661.286</v>
+        <v>1686.457</v>
       </c>
       <c r="G68">
         <v>105.7</v>
@@ -6857,45 +6857,45 @@
         <v>253.886</v>
       </c>
       <c r="M68">
-        <v>125.9254788</v>
+        <v>151.78113</v>
       </c>
       <c r="N68">
-        <v>127.9605212</v>
+        <v>102.10487</v>
       </c>
       <c r="O68">
-        <v>19.19407817999999</v>
+        <v>15.3157305</v>
       </c>
       <c r="P68">
-        <v>108.76644302</v>
+        <v>86.7891395</v>
       </c>
       <c r="Q68">
-        <v>109.25544302</v>
+        <v>87.27813950000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1609044509024015</v>
+        <v>0.164195029830429</v>
       </c>
       <c r="T68">
-        <v>1.500196860077333</v>
+        <v>1.543084134522083</v>
       </c>
       <c r="U68">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V68">
         <v>0.15</v>
       </c>
       <c r="W68">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.01616068820538</v>
+        <v>1.67271122569716</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1054393598440416</v>
+        <v>0.1056812063812666</v>
       </c>
       <c r="C69">
-        <v>452.7296498467547</v>
+        <v>419.3458609856293</v>
       </c>
       <c r="D69">
-        <v>2033.486649846755</v>
+        <v>2025.27386098563</v>
       </c>
       <c r="E69">
-        <v>721.6570000000002</v>
+        <v>746.8280000000002</v>
       </c>
       <c r="F69">
-        <v>1686.457</v>
+        <v>1711.628</v>
       </c>
       <c r="G69">
         <v>105.7</v>
@@ -6939,28 +6939,28 @@
         <v>253.886</v>
       </c>
       <c r="M69">
-        <v>151.78113</v>
+        <v>154.04652</v>
       </c>
       <c r="N69">
-        <v>102.10487</v>
+        <v>99.83947999999998</v>
       </c>
       <c r="O69">
-        <v>15.3157305</v>
+        <v>14.975922</v>
       </c>
       <c r="P69">
-        <v>86.7891395</v>
+        <v>84.86355799999998</v>
       </c>
       <c r="Q69">
-        <v>87.27813950000001</v>
+        <v>85.35255799999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.164195029830429</v>
+        <v>0.1676912699414582</v>
       </c>
       <c r="T69">
-        <v>1.543084134522083</v>
+        <v>1.588651863619629</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.67271122569716</v>
+        <v>1.648112531201614</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1056812063812666</v>
+        <v>0.1059230529184917</v>
       </c>
       <c r="C70">
-        <v>419.3458609856293</v>
+        <v>386.0281444362249</v>
       </c>
       <c r="D70">
-        <v>2025.27386098563</v>
+        <v>2017.127144436225</v>
       </c>
       <c r="E70">
-        <v>746.8280000000002</v>
+        <v>771.999</v>
       </c>
       <c r="F70">
-        <v>1711.628</v>
+        <v>1736.799</v>
       </c>
       <c r="G70">
         <v>105.7</v>
@@ -7021,28 +7021,28 @@
         <v>253.886</v>
       </c>
       <c r="M70">
-        <v>154.04652</v>
+        <v>156.31191</v>
       </c>
       <c r="N70">
-        <v>99.83947999999998</v>
+        <v>97.57409000000001</v>
       </c>
       <c r="O70">
-        <v>14.975922</v>
+        <v>14.6361135</v>
       </c>
       <c r="P70">
-        <v>84.86355799999998</v>
+        <v>82.93797650000002</v>
       </c>
       <c r="Q70">
-        <v>85.35255799999999</v>
+        <v>83.42697650000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1676912699414582</v>
+        <v>0.1714130739306184</v>
       </c>
       <c r="T70">
-        <v>1.588651863619629</v>
+        <v>1.63715944620734</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.648112531201614</v>
+        <v>1.624226842343619</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1059230529184917</v>
+        <v>0.1061648994557167</v>
       </c>
       <c r="C71">
-        <v>386.0281444362249</v>
+        <v>352.7757060602287</v>
       </c>
       <c r="D71">
-        <v>2017.127144436225</v>
+        <v>2009.045706060229</v>
       </c>
       <c r="E71">
-        <v>771.999</v>
+        <v>797.1700000000001</v>
       </c>
       <c r="F71">
-        <v>1736.799</v>
+        <v>1761.97</v>
       </c>
       <c r="G71">
         <v>105.7</v>
@@ -7103,28 +7103,28 @@
         <v>253.886</v>
       </c>
       <c r="M71">
-        <v>156.31191</v>
+        <v>158.5773</v>
       </c>
       <c r="N71">
-        <v>97.57409000000001</v>
+        <v>95.30869999999999</v>
       </c>
       <c r="O71">
-        <v>14.6361135</v>
+        <v>14.296305</v>
       </c>
       <c r="P71">
-        <v>82.93797650000002</v>
+        <v>81.01239499999998</v>
       </c>
       <c r="Q71">
-        <v>83.42697650000002</v>
+        <v>81.50139499999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1714130739306184</v>
+        <v>0.1753829981857225</v>
       </c>
       <c r="T71">
-        <v>1.63715944620734</v>
+        <v>1.688900867634231</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.624226842343619</v>
+        <v>1.60102360173871</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1061648994557167</v>
+        <v>0.1064067459929418</v>
       </c>
       <c r="C72">
-        <v>352.7757060602287</v>
+        <v>319.5877643951194</v>
       </c>
       <c r="D72">
-        <v>2009.045706060229</v>
+        <v>2001.02876439512</v>
       </c>
       <c r="E72">
-        <v>797.1700000000001</v>
+        <v>822.3410000000001</v>
       </c>
       <c r="F72">
-        <v>1761.97</v>
+        <v>1787.141</v>
       </c>
       <c r="G72">
         <v>105.7</v>
@@ -7185,28 +7185,28 @@
         <v>253.886</v>
       </c>
       <c r="M72">
-        <v>158.5773</v>
+        <v>160.84269</v>
       </c>
       <c r="N72">
-        <v>95.30869999999999</v>
+        <v>93.04330999999999</v>
       </c>
       <c r="O72">
-        <v>14.296305</v>
+        <v>13.9564965</v>
       </c>
       <c r="P72">
-        <v>81.01239499999998</v>
+        <v>79.08681349999999</v>
       </c>
       <c r="Q72">
-        <v>81.50139499999999</v>
+        <v>79.5758135</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1753829981857225</v>
+        <v>0.179626710320489</v>
       </c>
       <c r="T72">
-        <v>1.688900867634231</v>
+        <v>1.744210662952632</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.60102360173871</v>
+        <v>1.578473973545207</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1064067459929418</v>
+        <v>0.1066485925301668</v>
       </c>
       <c r="C73">
-        <v>319.5877643951196</v>
+        <v>286.4635504022613</v>
       </c>
       <c r="D73">
-        <v>2001.02876439512</v>
+        <v>1993.075550402261</v>
       </c>
       <c r="E73">
-        <v>822.3409999999999</v>
+        <v>847.5119999999999</v>
       </c>
       <c r="F73">
-        <v>1787.141</v>
+        <v>1812.312</v>
       </c>
       <c r="G73">
         <v>105.7</v>
@@ -7267,28 +7267,28 @@
         <v>253.886</v>
       </c>
       <c r="M73">
-        <v>160.84269</v>
+        <v>163.10808</v>
       </c>
       <c r="N73">
-        <v>93.04331000000002</v>
+        <v>90.77792000000002</v>
       </c>
       <c r="O73">
-        <v>13.9564965</v>
+        <v>13.616688</v>
       </c>
       <c r="P73">
-        <v>79.08681350000002</v>
+        <v>77.16123200000001</v>
       </c>
       <c r="Q73">
-        <v>79.57581350000002</v>
+        <v>77.65023200000002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1796267103204889</v>
+        <v>0.1841735447505959</v>
       </c>
       <c r="T73">
-        <v>1.744210662952631</v>
+        <v>1.803471157936632</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.578473973545208</v>
+        <v>1.556550723912635</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1066485925301668</v>
+        <v>0.1068904390673919</v>
       </c>
       <c r="C74">
-        <v>286.4635504022613</v>
+        <v>253.4023072209841</v>
       </c>
       <c r="D74">
-        <v>1993.075550402261</v>
+        <v>1985.185307220984</v>
       </c>
       <c r="E74">
-        <v>847.5119999999999</v>
+        <v>872.683</v>
       </c>
       <c r="F74">
-        <v>1812.312</v>
+        <v>1837.483</v>
       </c>
       <c r="G74">
         <v>105.7</v>
@@ -7349,28 +7349,28 @@
         <v>253.886</v>
       </c>
       <c r="M74">
-        <v>163.10808</v>
+        <v>165.37347</v>
       </c>
       <c r="N74">
-        <v>90.77792000000002</v>
+        <v>88.51253</v>
       </c>
       <c r="O74">
-        <v>13.616688</v>
+        <v>13.2768795</v>
       </c>
       <c r="P74">
-        <v>77.16123200000001</v>
+        <v>75.23565049999999</v>
       </c>
       <c r="Q74">
-        <v>77.65023200000002</v>
+        <v>75.7246505</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1841735447505959</v>
+        <v>0.1890571817310811</v>
       </c>
       <c r="T74">
-        <v>1.803471157936632</v>
+        <v>1.867121319215745</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.556550723912635</v>
+        <v>1.535228111256298</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1068904390673919</v>
+        <v>0.107132285604617</v>
       </c>
       <c r="C75">
-        <v>253.4023072209841</v>
+        <v>220.4032899284844</v>
       </c>
       <c r="D75">
-        <v>1985.185307220984</v>
+        <v>1977.357289928484</v>
       </c>
       <c r="E75">
-        <v>872.683</v>
+        <v>897.854</v>
       </c>
       <c r="F75">
-        <v>1837.483</v>
+        <v>1862.654</v>
       </c>
       <c r="G75">
         <v>105.7</v>
@@ -7431,28 +7431,28 @@
         <v>253.886</v>
       </c>
       <c r="M75">
-        <v>165.37347</v>
+        <v>167.63886</v>
       </c>
       <c r="N75">
-        <v>88.51253</v>
+        <v>86.24714</v>
       </c>
       <c r="O75">
-        <v>13.2768795</v>
+        <v>12.937071</v>
       </c>
       <c r="P75">
-        <v>75.23565049999999</v>
+        <v>73.310069</v>
       </c>
       <c r="Q75">
-        <v>75.7246505</v>
+        <v>73.799069</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1890571817310811</v>
+        <v>0.1943164830946806</v>
       </c>
       <c r="T75">
-        <v>1.867121319215745</v>
+        <v>1.935667646747096</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.535228111256298</v>
+        <v>1.51448178542851</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.107132285604617</v>
+        <v>0.1453793539680453</v>
       </c>
       <c r="C76">
-        <v>220.4032899284844</v>
+        <v>-564.2436097754537</v>
       </c>
       <c r="D76">
-        <v>1977.357289928484</v>
+        <v>1217.881390224546</v>
       </c>
       <c r="E76">
-        <v>897.854</v>
+        <v>923.0249999999999</v>
       </c>
       <c r="F76">
-        <v>1862.654</v>
+        <v>1887.825</v>
       </c>
       <c r="G76">
         <v>105.7</v>
@@ -7513,45 +7513,45 @@
         <v>253.886</v>
       </c>
       <c r="M76">
-        <v>167.63886</v>
+        <v>277.13271</v>
       </c>
       <c r="N76">
-        <v>86.24714</v>
+        <v>-23.24670999999998</v>
       </c>
       <c r="O76">
-        <v>12.937071</v>
+        <v>-3.487006499999997</v>
       </c>
       <c r="P76">
-        <v>73.310069</v>
+        <v>-19.75970349999998</v>
       </c>
       <c r="Q76">
-        <v>73.799069</v>
+        <v>-19.27070349999998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1943164830946806</v>
+        <v>0.2016361080179045</v>
       </c>
       <c r="T76">
-        <v>1.935667646747096</v>
+        <v>2.031066897086035</v>
       </c>
       <c r="U76">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.15</v>
+        <v>0.1374175570974643</v>
       </c>
       <c r="W76">
-        <v>0.0765</v>
+        <v>0.1266271026180923</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y76">
-        <v>1.51448178542851</v>
+        <v>0.9161170473164284</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1453793539680453</v>
+        <v>0.1463893539680453</v>
       </c>
       <c r="C77">
-        <v>-564.2436097754537</v>
+        <v>-601.6431424740294</v>
       </c>
       <c r="D77">
-        <v>1217.881390224546</v>
+        <v>1205.65285752597</v>
       </c>
       <c r="E77">
-        <v>923.0249999999999</v>
+        <v>948.1959999999999</v>
       </c>
       <c r="F77">
-        <v>1887.825</v>
+        <v>1912.996</v>
       </c>
       <c r="G77">
         <v>105.7</v>
@@ -7595,37 +7595,37 @@
         <v>253.886</v>
       </c>
       <c r="M77">
-        <v>277.13271</v>
+        <v>280.8278128</v>
       </c>
       <c r="N77">
-        <v>-23.24670999999998</v>
+        <v>-26.94181280000001</v>
       </c>
       <c r="O77">
-        <v>-3.487006499999997</v>
+        <v>-4.041271920000001</v>
       </c>
       <c r="P77">
-        <v>-19.75970349999998</v>
+        <v>-22.90054088000001</v>
       </c>
       <c r="Q77">
-        <v>-19.27070349999998</v>
+        <v>-22.41154088000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2016361080179045</v>
+        <v>0.2081292791853172</v>
       </c>
       <c r="T77">
-        <v>2.031066897086035</v>
+        <v>2.11569468446462</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1374175570974643</v>
+        <v>0.1356094313461818</v>
       </c>
       <c r="W77">
-        <v>0.1266271026180923</v>
+        <v>0.1268925354783805</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.9161170473164284</v>
+        <v>0.9040628756412121</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1463893539680453</v>
+        <v>0.1473993539680453</v>
       </c>
       <c r="C78">
-        <v>-601.6431424740294</v>
+        <v>-638.79954728757</v>
       </c>
       <c r="D78">
-        <v>1205.65285752597</v>
+        <v>1193.66745271243</v>
       </c>
       <c r="E78">
-        <v>948.1959999999999</v>
+        <v>973.367</v>
       </c>
       <c r="F78">
-        <v>1912.996</v>
+        <v>1938.167</v>
       </c>
       <c r="G78">
         <v>105.7</v>
@@ -7677,37 +7677,37 @@
         <v>253.886</v>
       </c>
       <c r="M78">
-        <v>280.8278128</v>
+        <v>284.5229156</v>
       </c>
       <c r="N78">
-        <v>-26.94181280000001</v>
+        <v>-30.63691560000004</v>
       </c>
       <c r="O78">
-        <v>-4.041271920000001</v>
+        <v>-4.595537340000005</v>
       </c>
       <c r="P78">
-        <v>-22.90054088000001</v>
+        <v>-26.04137826000003</v>
       </c>
       <c r="Q78">
-        <v>-22.41154088000001</v>
+        <v>-25.55237826000003</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2081292791853172</v>
+        <v>0.2151870739325049</v>
       </c>
       <c r="T78">
-        <v>2.11569468446462</v>
+        <v>2.207681409876125</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1356094313461818</v>
+        <v>0.1338482699001275</v>
       </c>
       <c r="W78">
-        <v>0.1268925354783805</v>
+        <v>0.1271510739786613</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.9040628756412121</v>
+        <v>0.8923217993341833</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1473993539680453</v>
+        <v>0.1484093539680453</v>
       </c>
       <c r="C79">
-        <v>-638.79954728757</v>
+        <v>-675.7200036540432</v>
       </c>
       <c r="D79">
-        <v>1193.66745271243</v>
+        <v>1181.917996345957</v>
       </c>
       <c r="E79">
-        <v>973.367</v>
+        <v>998.538</v>
       </c>
       <c r="F79">
-        <v>1938.167</v>
+        <v>1963.338</v>
       </c>
       <c r="G79">
         <v>105.7</v>
@@ -7759,37 +7759,37 @@
         <v>253.886</v>
       </c>
       <c r="M79">
-        <v>284.5229156</v>
+        <v>288.2180184</v>
       </c>
       <c r="N79">
-        <v>-30.63691560000004</v>
+        <v>-34.33201840000001</v>
       </c>
       <c r="O79">
-        <v>-4.595537340000005</v>
+        <v>-5.149802760000001</v>
       </c>
       <c r="P79">
-        <v>-26.04137826000003</v>
+        <v>-29.18221564000001</v>
       </c>
       <c r="Q79">
-        <v>-25.55237826000003</v>
+        <v>-28.69321564000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2151870739325049</v>
+        <v>0.2228864863839824</v>
       </c>
       <c r="T79">
-        <v>2.207681409876125</v>
+        <v>2.308030564870495</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1338482699001275</v>
+        <v>0.1321322664398695</v>
       </c>
       <c r="W79">
-        <v>0.1271510739786613</v>
+        <v>0.1274029832866272</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8923217993341833</v>
+        <v>0.8808817762657964</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1484093539680453</v>
+        <v>0.1494193539680453</v>
       </c>
       <c r="C80">
-        <v>-675.7200036540432</v>
+        <v>-712.4114110933481</v>
       </c>
       <c r="D80">
-        <v>1181.917996345957</v>
+        <v>1170.397588906652</v>
       </c>
       <c r="E80">
-        <v>998.538</v>
+        <v>1023.709</v>
       </c>
       <c r="F80">
-        <v>1963.338</v>
+        <v>1988.509</v>
       </c>
       <c r="G80">
         <v>105.7</v>
@@ -7841,37 +7841,37 @@
         <v>253.886</v>
       </c>
       <c r="M80">
-        <v>288.2180184</v>
+        <v>291.9131212</v>
       </c>
       <c r="N80">
-        <v>-34.33201840000001</v>
+        <v>-38.02712120000004</v>
       </c>
       <c r="O80">
-        <v>-5.149802760000001</v>
+        <v>-5.704068180000005</v>
       </c>
       <c r="P80">
-        <v>-29.18221564000001</v>
+        <v>-32.32305302000003</v>
       </c>
       <c r="Q80">
-        <v>-28.69321564000001</v>
+        <v>-31.83405302000003</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2228864863839824</v>
+        <v>0.2313191762117911</v>
       </c>
       <c r="T80">
-        <v>2.308030564870495</v>
+        <v>2.41793678224528</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1321322664398695</v>
+        <v>0.1304597061051875</v>
       </c>
       <c r="W80">
-        <v>0.1274029832866272</v>
+        <v>0.1276485151437585</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8808817762657964</v>
+        <v>0.8697313740345837</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1494193539680453</v>
+        <v>0.1504293539680454</v>
       </c>
       <c r="C81">
-        <v>-712.4114110933481</v>
+        <v>-748.8804027177327</v>
       </c>
       <c r="D81">
-        <v>1170.397588906652</v>
+        <v>1159.099597282267</v>
       </c>
       <c r="E81">
-        <v>1023.709</v>
+        <v>1048.88</v>
       </c>
       <c r="F81">
-        <v>1988.509</v>
+        <v>2013.68</v>
       </c>
       <c r="G81">
         <v>105.7</v>
@@ -7923,37 +7923,37 @@
         <v>253.886</v>
       </c>
       <c r="M81">
-        <v>291.9131212</v>
+        <v>295.6082240000001</v>
       </c>
       <c r="N81">
-        <v>-38.02712120000004</v>
+        <v>-41.72222400000007</v>
       </c>
       <c r="O81">
-        <v>-5.704068180000005</v>
+        <v>-6.25833360000001</v>
       </c>
       <c r="P81">
-        <v>-32.32305302000003</v>
+        <v>-35.46389040000006</v>
       </c>
       <c r="Q81">
-        <v>-31.83405302000003</v>
+        <v>-34.97489040000006</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2313191762117911</v>
+        <v>0.2405951350223807</v>
       </c>
       <c r="T81">
-        <v>2.41793678224528</v>
+        <v>2.538833621357545</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1304597061051875</v>
+        <v>0.1288289597788727</v>
       </c>
       <c r="W81">
-        <v>0.1276485151437585</v>
+        <v>0.1278879087044615</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8697313740345837</v>
+        <v>0.8588597318591513</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1504293539680454</v>
+        <v>0.1514393539680453</v>
       </c>
       <c r="C82">
-        <v>-748.8804027177327</v>
+        <v>-785.1333579671859</v>
       </c>
       <c r="D82">
-        <v>1159.099597282267</v>
+        <v>1148.017642032814</v>
       </c>
       <c r="E82">
-        <v>1048.88</v>
+        <v>1074.051</v>
       </c>
       <c r="F82">
-        <v>2013.68</v>
+        <v>2038.851</v>
       </c>
       <c r="G82">
         <v>105.7</v>
@@ -8005,37 +8005,37 @@
         <v>253.886</v>
       </c>
       <c r="M82">
-        <v>295.6082240000001</v>
+        <v>299.3033268</v>
       </c>
       <c r="N82">
-        <v>-41.72222400000007</v>
+        <v>-45.41732680000004</v>
       </c>
       <c r="O82">
-        <v>-6.25833360000001</v>
+        <v>-6.812599020000006</v>
       </c>
       <c r="P82">
-        <v>-35.46389040000006</v>
+        <v>-38.60472778000003</v>
       </c>
       <c r="Q82">
-        <v>-34.97489040000006</v>
+        <v>-38.11572778000004</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2405951350223807</v>
+        <v>0.2508475105498744</v>
       </c>
       <c r="T82">
-        <v>2.538833621357545</v>
+        <v>2.672456443534257</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1288289597788727</v>
+        <v>0.1272384787939483</v>
       </c>
       <c r="W82">
-        <v>0.1278879087044615</v>
+        <v>0.1281213913130484</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8588597318591513</v>
+        <v>0.848256525292989</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1514393539680453</v>
+        <v>0.1524493539680453</v>
       </c>
       <c r="C83">
-        <v>-785.1333579671859</v>
+        <v>-821.1764146211865</v>
       </c>
       <c r="D83">
-        <v>1148.017642032814</v>
+        <v>1137.145585378813</v>
       </c>
       <c r="E83">
-        <v>1074.051</v>
+        <v>1099.222</v>
       </c>
       <c r="F83">
-        <v>2038.851</v>
+        <v>2064.022</v>
       </c>
       <c r="G83">
         <v>105.7</v>
@@ -8087,37 +8087,37 @@
         <v>253.886</v>
       </c>
       <c r="M83">
-        <v>299.3033268</v>
+        <v>302.9984296</v>
       </c>
       <c r="N83">
-        <v>-45.41732680000004</v>
+        <v>-49.11242960000001</v>
       </c>
       <c r="O83">
-        <v>-6.812599020000006</v>
+        <v>-7.366864440000001</v>
       </c>
       <c r="P83">
-        <v>-38.60472778000003</v>
+        <v>-41.74556516000001</v>
       </c>
       <c r="Q83">
-        <v>-38.11572778000004</v>
+        <v>-41.25656516000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2508475105498744</v>
+        <v>0.2622390389137563</v>
       </c>
       <c r="T83">
-        <v>2.672456443534257</v>
+        <v>2.820926245952827</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1272384787939483</v>
+        <v>0.1256867900281685</v>
       </c>
       <c r="W83">
-        <v>0.1281213913130484</v>
+        <v>0.1283491792238649</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.848256525292989</v>
+        <v>0.8379119335211234</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1524493539680453</v>
+        <v>0.1534593539680453</v>
       </c>
       <c r="C84">
-        <v>-821.1764146211865</v>
+        <v>-857.015480134319</v>
       </c>
       <c r="D84">
-        <v>1137.145585378813</v>
+        <v>1126.477519865681</v>
       </c>
       <c r="E84">
-        <v>1099.222</v>
+        <v>1124.393</v>
       </c>
       <c r="F84">
-        <v>2064.022</v>
+        <v>2089.193</v>
       </c>
       <c r="G84">
         <v>105.7</v>
@@ -8169,37 +8169,37 @@
         <v>253.886</v>
       </c>
       <c r="M84">
-        <v>302.9984296</v>
+        <v>306.6935324</v>
       </c>
       <c r="N84">
-        <v>-49.11242960000001</v>
+        <v>-52.80753240000004</v>
       </c>
       <c r="O84">
-        <v>-7.366864440000001</v>
+        <v>-7.921129860000006</v>
       </c>
       <c r="P84">
-        <v>-41.74556516000001</v>
+        <v>-44.88640254000003</v>
       </c>
       <c r="Q84">
-        <v>-41.25656516000002</v>
+        <v>-44.39740254000004</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2622390389137563</v>
+        <v>0.2749707470851537</v>
       </c>
       <c r="T84">
-        <v>2.820926245952827</v>
+        <v>2.986863083950052</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1256867900281685</v>
+        <v>0.1241724913531303</v>
       </c>
       <c r="W84">
-        <v>0.1283491792238649</v>
+        <v>0.1285714782693605</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8379119335211234</v>
+        <v>0.8278166090208688</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1534593539680453</v>
+        <v>0.1544693539680453</v>
       </c>
       <c r="C85">
-        <v>-857.015480134319</v>
+        <v>-892.6562423397597</v>
       </c>
       <c r="D85">
-        <v>1126.477519865681</v>
+        <v>1116.00775766024</v>
       </c>
       <c r="E85">
-        <v>1124.393</v>
+        <v>1149.564</v>
       </c>
       <c r="F85">
-        <v>2089.193</v>
+        <v>2114.364</v>
       </c>
       <c r="G85">
         <v>105.7</v>
@@ -8251,37 +8251,37 @@
         <v>253.886</v>
       </c>
       <c r="M85">
-        <v>306.6935324</v>
+        <v>310.3886352</v>
       </c>
       <c r="N85">
-        <v>-52.80753240000004</v>
+        <v>-56.50263520000001</v>
       </c>
       <c r="O85">
-        <v>-7.921129860000006</v>
+        <v>-8.475395280000003</v>
       </c>
       <c r="P85">
-        <v>-44.88640254000003</v>
+        <v>-48.02723992000001</v>
       </c>
       <c r="Q85">
-        <v>-44.39740254000004</v>
+        <v>-47.53823992000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2749707470851537</v>
+        <v>0.2892939187779759</v>
       </c>
       <c r="T85">
-        <v>2.986863083950052</v>
+        <v>3.173542026696932</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1241724913531303</v>
+        <v>0.1226942474084502</v>
       </c>
       <c r="W85">
-        <v>0.1285714782693605</v>
+        <v>0.1287884844804395</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8278166090208688</v>
+        <v>0.8179616493896681</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1544693539680453</v>
+        <v>0.1554793539680453</v>
       </c>
       <c r="C86">
-        <v>-892.6562423397595</v>
+        <v>-928.1041795613744</v>
       </c>
       <c r="D86">
-        <v>1116.00775766024</v>
+        <v>1105.730820438625</v>
       </c>
       <c r="E86">
-        <v>1149.564</v>
+        <v>1174.735</v>
       </c>
       <c r="F86">
-        <v>2114.364</v>
+        <v>2139.535</v>
       </c>
       <c r="G86">
         <v>105.7</v>
@@ -8333,37 +8333,37 @@
         <v>253.886</v>
       </c>
       <c r="M86">
-        <v>310.3886352</v>
+        <v>314.083738</v>
       </c>
       <c r="N86">
-        <v>-56.50263520000001</v>
+        <v>-60.19773799999999</v>
       </c>
       <c r="O86">
-        <v>-8.475395280000003</v>
+        <v>-9.029660699999997</v>
       </c>
       <c r="P86">
-        <v>-48.02723992000001</v>
+        <v>-51.16807729999999</v>
       </c>
       <c r="Q86">
-        <v>-47.53823992000002</v>
+        <v>-50.6790773</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2892939187779757</v>
+        <v>0.3055268466965075</v>
       </c>
       <c r="T86">
-        <v>3.173542026696929</v>
+        <v>3.385111495143391</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1226942474084502</v>
+        <v>0.1212507856742332</v>
       </c>
       <c r="W86">
-        <v>0.1287884844804395</v>
+        <v>0.1290003846630226</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8179616493896681</v>
+        <v>0.8083385711615544</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1554793539680453</v>
+        <v>0.204133224494222</v>
       </c>
       <c r="C87">
-        <v>-928.1041795613744</v>
+        <v>-1293.052786859375</v>
       </c>
       <c r="D87">
-        <v>1105.730820438625</v>
+        <v>765.9532131406245</v>
       </c>
       <c r="E87">
-        <v>1174.735</v>
+        <v>1199.906</v>
       </c>
       <c r="F87">
-        <v>2139.535</v>
+        <v>2164.706</v>
       </c>
       <c r="G87">
         <v>105.7</v>
@@ -8415,45 +8415,45 @@
         <v>253.886</v>
       </c>
       <c r="M87">
-        <v>314.083738</v>
+        <v>434.6729647999999</v>
       </c>
       <c r="N87">
-        <v>-60.19773799999999</v>
+        <v>-180.7869647999999</v>
       </c>
       <c r="O87">
-        <v>-9.029660699999997</v>
+        <v>-27.11804471999999</v>
       </c>
       <c r="P87">
-        <v>-51.16807729999999</v>
+        <v>-153.6689200799999</v>
       </c>
       <c r="Q87">
-        <v>-50.6790773</v>
+        <v>-153.1799200799999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3055268466965075</v>
+        <v>0.3326778395046631</v>
       </c>
       <c r="T87">
-        <v>3.385111495143391</v>
+        <v>3.738979949746544</v>
       </c>
       <c r="U87">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1212507856742332</v>
+        <v>0.08761276427100212</v>
       </c>
       <c r="W87">
-        <v>0.1290003846630226</v>
+        <v>0.1832073569343828</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.8083385711615544</v>
+        <v>0.5840850951400142</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.204133224494222</v>
+        <v>0.205683224494222</v>
       </c>
       <c r="C88">
-        <v>-1293.052786859375</v>
+        <v>-1325.649378156547</v>
       </c>
       <c r="D88">
-        <v>765.9532131406245</v>
+        <v>758.5276218434533</v>
       </c>
       <c r="E88">
-        <v>1199.906</v>
+        <v>1225.077</v>
       </c>
       <c r="F88">
-        <v>2164.706</v>
+        <v>2189.877</v>
       </c>
       <c r="G88">
         <v>105.7</v>
@@ -8497,37 +8497,37 @@
         <v>253.886</v>
       </c>
       <c r="M88">
-        <v>434.6729647999999</v>
+        <v>439.7273016</v>
       </c>
       <c r="N88">
-        <v>-180.7869647999999</v>
+        <v>-185.8413016</v>
       </c>
       <c r="O88">
-        <v>-27.11804471999999</v>
+        <v>-27.87619524</v>
       </c>
       <c r="P88">
-        <v>-153.6689200799999</v>
+        <v>-157.96510636</v>
       </c>
       <c r="Q88">
-        <v>-153.1799200799999</v>
+        <v>-157.47610636</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3326778395046631</v>
+        <v>0.3547453656204064</v>
       </c>
       <c r="T88">
-        <v>3.738979949746544</v>
+        <v>4.026593792034739</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.08761276427100212</v>
+        <v>0.08660572100351932</v>
       </c>
       <c r="W88">
-        <v>0.1832073569343828</v>
+        <v>0.1834095712224933</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5840850951400142</v>
+        <v>0.5773714733567955</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.205683224494222</v>
+        <v>0.207233224494222</v>
       </c>
       <c r="C89">
-        <v>-1325.649378156547</v>
+        <v>-1358.103375925692</v>
       </c>
       <c r="D89">
-        <v>758.5276218434533</v>
+        <v>751.2446240743078</v>
       </c>
       <c r="E89">
-        <v>1225.077</v>
+        <v>1250.248</v>
       </c>
       <c r="F89">
-        <v>2189.877</v>
+        <v>2215.048</v>
       </c>
       <c r="G89">
         <v>105.7</v>
@@ -8579,37 +8579,37 @@
         <v>253.886</v>
       </c>
       <c r="M89">
-        <v>439.7273016</v>
+        <v>444.7816384</v>
       </c>
       <c r="N89">
-        <v>-185.8413016</v>
+        <v>-190.8956384</v>
       </c>
       <c r="O89">
-        <v>-27.87619524</v>
+        <v>-28.63434576</v>
       </c>
       <c r="P89">
-        <v>-157.96510636</v>
+        <v>-162.26129264</v>
       </c>
       <c r="Q89">
-        <v>-157.47610636</v>
+        <v>-161.77229264</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3547453656204064</v>
+        <v>0.3804908127554403</v>
       </c>
       <c r="T89">
-        <v>4.026593792034739</v>
+        <v>4.362143274704302</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.08660572100351932</v>
+        <v>0.08562156508302479</v>
       </c>
       <c r="W89">
-        <v>0.1834095712224933</v>
+        <v>0.1836071897313286</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5773714733567955</v>
+        <v>0.5708104338868321</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.207233224494222</v>
+        <v>0.208783224494222</v>
       </c>
       <c r="C90">
-        <v>-1358.103375925692</v>
+        <v>-1390.418848437686</v>
       </c>
       <c r="D90">
-        <v>751.2446240743078</v>
+        <v>744.1001515623136</v>
       </c>
       <c r="E90">
-        <v>1250.248</v>
+        <v>1275.419</v>
       </c>
       <c r="F90">
-        <v>2215.048</v>
+        <v>2240.219</v>
       </c>
       <c r="G90">
         <v>105.7</v>
@@ -8661,37 +8661,37 @@
         <v>253.886</v>
       </c>
       <c r="M90">
-        <v>444.7816384</v>
+        <v>449.8359752</v>
       </c>
       <c r="N90">
-        <v>-190.8956384</v>
+        <v>-195.9499752</v>
       </c>
       <c r="O90">
-        <v>-28.63434576</v>
+        <v>-29.39249628</v>
       </c>
       <c r="P90">
-        <v>-162.26129264</v>
+        <v>-166.55747892</v>
       </c>
       <c r="Q90">
-        <v>-161.77229264</v>
+        <v>-166.06847892</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3804908127554403</v>
+        <v>0.4109172502786621</v>
       </c>
       <c r="T90">
-        <v>4.362143274704302</v>
+        <v>4.758701754222875</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.08562156508302479</v>
+        <v>0.08465952502591216</v>
       </c>
       <c r="W90">
-        <v>0.1836071897313286</v>
+        <v>0.1838003673747969</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5708104338868321</v>
+        <v>0.5643968335060809</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.208783224494222</v>
+        <v>0.210333224494222</v>
       </c>
       <c r="C91">
-        <v>-1390.418848437686</v>
+        <v>-1422.599710661362</v>
       </c>
       <c r="D91">
-        <v>744.1001515623136</v>
+        <v>737.0902893386378</v>
       </c>
       <c r="E91">
-        <v>1275.419</v>
+        <v>1300.59</v>
       </c>
       <c r="F91">
-        <v>2240.219</v>
+        <v>2265.39</v>
       </c>
       <c r="G91">
         <v>105.7</v>
@@ -8743,37 +8743,37 @@
         <v>253.886</v>
       </c>
       <c r="M91">
-        <v>449.8359752</v>
+        <v>454.890312</v>
       </c>
       <c r="N91">
-        <v>-195.9499752</v>
+        <v>-201.004312</v>
       </c>
       <c r="O91">
-        <v>-29.39249628</v>
+        <v>-30.1506468</v>
       </c>
       <c r="P91">
-        <v>-166.55747892</v>
+        <v>-170.8536652</v>
       </c>
       <c r="Q91">
-        <v>-166.06847892</v>
+        <v>-170.3646652</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4109172502786621</v>
+        <v>0.4474289753065284</v>
       </c>
       <c r="T91">
-        <v>4.758701754222875</v>
+        <v>5.234571929645162</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.08465952502591216</v>
+        <v>0.08371886363673535</v>
       </c>
       <c r="W91">
-        <v>0.1838003673747969</v>
+        <v>0.1839892521817436</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5643968335060809</v>
+        <v>0.5581257575782357</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.210333224494222</v>
+        <v>0.211883224494222</v>
       </c>
       <c r="C92">
-        <v>-1422.599710661362</v>
+        <v>-1454.649731417096</v>
       </c>
       <c r="D92">
-        <v>737.0902893386378</v>
+        <v>730.2112685829044</v>
       </c>
       <c r="E92">
-        <v>1300.59</v>
+        <v>1325.761</v>
       </c>
       <c r="F92">
-        <v>2265.39</v>
+        <v>2290.561</v>
       </c>
       <c r="G92">
         <v>105.7</v>
@@ -8825,37 +8825,37 @@
         <v>253.886</v>
       </c>
       <c r="M92">
-        <v>454.890312</v>
+        <v>459.9446488</v>
       </c>
       <c r="N92">
-        <v>-201.004312</v>
+        <v>-206.0586488</v>
       </c>
       <c r="O92">
-        <v>-30.1506468</v>
+        <v>-30.90879732000001</v>
       </c>
       <c r="P92">
-        <v>-170.8536652</v>
+        <v>-175.1498514800001</v>
       </c>
       <c r="Q92">
-        <v>-170.3646652</v>
+        <v>-174.66085148</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4474289753065284</v>
+        <v>0.4920544170072538</v>
       </c>
       <c r="T92">
-        <v>5.234571929645162</v>
+        <v>5.816191032939071</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.08371886363673535</v>
+        <v>0.08279887612424375</v>
       </c>
       <c r="W92">
-        <v>0.1839892521817436</v>
+        <v>0.1841739856742519</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5581257575782357</v>
+        <v>0.5519925074949583</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.211883224494222</v>
+        <v>0.213433224494222</v>
       </c>
       <c r="C93">
-        <v>-1454.649731417096</v>
+        <v>-1486.572540133526</v>
       </c>
       <c r="D93">
-        <v>730.2112685829044</v>
+        <v>723.4594598664736</v>
       </c>
       <c r="E93">
-        <v>1325.761</v>
+        <v>1350.932</v>
       </c>
       <c r="F93">
-        <v>2290.561</v>
+        <v>2315.732</v>
       </c>
       <c r="G93">
         <v>105.7</v>
@@ -8907,37 +8907,37 @@
         <v>253.886</v>
       </c>
       <c r="M93">
-        <v>459.9446488</v>
+        <v>464.9989856</v>
       </c>
       <c r="N93">
-        <v>-206.0586488</v>
+        <v>-211.1129856</v>
       </c>
       <c r="O93">
-        <v>-30.90879732000001</v>
+        <v>-31.66694784</v>
       </c>
       <c r="P93">
-        <v>-175.1498514800001</v>
+        <v>-179.44603776</v>
       </c>
       <c r="Q93">
-        <v>-174.66085148</v>
+        <v>-178.95703776</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4920544170072538</v>
+        <v>0.5478362191331606</v>
       </c>
       <c r="T93">
-        <v>5.816191032939071</v>
+        <v>6.543214912056456</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.08279887612424375</v>
+        <v>0.08189888834028457</v>
       </c>
       <c r="W93">
-        <v>0.1841739856742519</v>
+        <v>0.1843547032212709</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5519925074949583</v>
+        <v>0.5459925889352305</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.213433224494222</v>
+        <v>0.214983224494222</v>
       </c>
       <c r="C94">
-        <v>-1486.572540133526</v>
+        <v>-1518.371633232859</v>
       </c>
       <c r="D94">
-        <v>723.4594598664736</v>
+        <v>716.8313667671408</v>
       </c>
       <c r="E94">
-        <v>1350.932</v>
+        <v>1376.103</v>
       </c>
       <c r="F94">
-        <v>2315.732</v>
+        <v>2340.903</v>
       </c>
       <c r="G94">
         <v>105.7</v>
@@ -8989,37 +8989,37 @@
         <v>253.886</v>
       </c>
       <c r="M94">
-        <v>464.9989856</v>
+        <v>470.0533224000001</v>
       </c>
       <c r="N94">
-        <v>-211.1129856</v>
+        <v>-216.1673224000001</v>
       </c>
       <c r="O94">
-        <v>-31.66694784</v>
+        <v>-32.42509836000001</v>
       </c>
       <c r="P94">
-        <v>-179.44603776</v>
+        <v>-183.7422240400001</v>
       </c>
       <c r="Q94">
-        <v>-178.95703776</v>
+        <v>-183.25322404</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5478362191331606</v>
+        <v>0.6195556790093265</v>
       </c>
       <c r="T94">
-        <v>6.543214912056456</v>
+        <v>7.477959899493094</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.08189888834028457</v>
+        <v>0.08101825513232452</v>
       </c>
       <c r="W94">
-        <v>0.1843547032212709</v>
+        <v>0.1845315343694292</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5459925889352305</v>
+        <v>0.5401217008821635</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.214983224494222</v>
+        <v>0.216533224494222</v>
       </c>
       <c r="C95">
-        <v>-1518.371633232859</v>
+        <v>-1550.050380168352</v>
       </c>
       <c r="D95">
-        <v>716.8313667671408</v>
+        <v>710.3236198316479</v>
       </c>
       <c r="E95">
-        <v>1376.103</v>
+        <v>1401.274</v>
       </c>
       <c r="F95">
-        <v>2340.903</v>
+        <v>2366.074</v>
       </c>
       <c r="G95">
         <v>105.7</v>
@@ -9071,37 +9071,37 @@
         <v>253.886</v>
       </c>
       <c r="M95">
-        <v>470.0533224000001</v>
+        <v>475.1076592</v>
       </c>
       <c r="N95">
-        <v>-216.1673224000001</v>
+        <v>-221.2216592</v>
       </c>
       <c r="O95">
-        <v>-32.42509836000001</v>
+        <v>-33.18324888</v>
       </c>
       <c r="P95">
-        <v>-183.7422240400001</v>
+        <v>-188.03841032</v>
       </c>
       <c r="Q95">
-        <v>-183.25322404</v>
+        <v>-187.54941032</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6195556790093265</v>
+        <v>0.715181625510881</v>
       </c>
       <c r="T95">
-        <v>7.477959899493094</v>
+        <v>8.72428654940861</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.08101825513232452</v>
+        <v>0.08015635880112959</v>
       </c>
       <c r="W95">
-        <v>0.1845315343694292</v>
+        <v>0.1847046031527332</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5401217008821635</v>
+        <v>0.534375725340864</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.216533224494222</v>
+        <v>0.218083224494222</v>
       </c>
       <c r="C96">
-        <v>-1550.050380168352</v>
+        <v>-1581.612029135895</v>
       </c>
       <c r="D96">
-        <v>710.3236198316479</v>
+        <v>703.9329708641046</v>
       </c>
       <c r="E96">
-        <v>1401.274</v>
+        <v>1426.445</v>
       </c>
       <c r="F96">
-        <v>2366.074</v>
+        <v>2391.245</v>
       </c>
       <c r="G96">
         <v>105.7</v>
@@ -9153,37 +9153,37 @@
         <v>253.886</v>
       </c>
       <c r="M96">
-        <v>475.1076592</v>
+        <v>480.161996</v>
       </c>
       <c r="N96">
-        <v>-221.2216592</v>
+        <v>-226.275996</v>
       </c>
       <c r="O96">
-        <v>-33.18324888</v>
+        <v>-33.94139939999999</v>
       </c>
       <c r="P96">
-        <v>-188.03841032</v>
+        <v>-192.3345966</v>
       </c>
       <c r="Q96">
-        <v>-187.54941032</v>
+        <v>-191.8455966</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.715181625510881</v>
+        <v>0.8490579506130577</v>
       </c>
       <c r="T96">
-        <v>8.72428654940861</v>
+        <v>10.46914385929034</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.08015635880112959</v>
+        <v>0.07931260765585453</v>
       </c>
       <c r="W96">
-        <v>0.1847046031527332</v>
+        <v>0.1848740283827044</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.534375725340864</v>
+        <v>0.5287507177056969</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.218083224494222</v>
+        <v>0.219633224494222</v>
       </c>
       <c r="C97">
-        <v>-1581.612029135895</v>
+        <v>-1613.059712480026</v>
       </c>
       <c r="D97">
-        <v>703.9329708641046</v>
+        <v>697.6562875199741</v>
       </c>
       <c r="E97">
-        <v>1426.445</v>
+        <v>1451.616</v>
       </c>
       <c r="F97">
-        <v>2391.245</v>
+        <v>2416.416</v>
       </c>
       <c r="G97">
         <v>105.7</v>
@@ -9235,37 +9235,37 @@
         <v>253.886</v>
       </c>
       <c r="M97">
-        <v>480.161996</v>
+        <v>485.2163328</v>
       </c>
       <c r="N97">
-        <v>-226.275996</v>
+        <v>-231.3303328</v>
       </c>
       <c r="O97">
-        <v>-33.94139939999999</v>
+        <v>-34.69954992</v>
       </c>
       <c r="P97">
-        <v>-192.3345966</v>
+        <v>-196.63078288</v>
       </c>
       <c r="Q97">
-        <v>-191.8455966</v>
+        <v>-196.14178288</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8490579506130577</v>
+        <v>1.049872438266323</v>
       </c>
       <c r="T97">
-        <v>10.46914385929034</v>
+        <v>13.08642982411293</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.07931260765585453</v>
+        <v>0.07848643465943937</v>
       </c>
       <c r="W97">
-        <v>0.1848740283827044</v>
+        <v>0.1850399239203846</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5287507177056969</v>
+        <v>0.523242897729596</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.219633224494222</v>
+        <v>0.221183224494222</v>
       </c>
       <c r="C98">
-        <v>-1613.059712480025</v>
+        <v>-1644.396451813274</v>
       </c>
       <c r="D98">
-        <v>697.6562875199743</v>
+        <v>691.4905481867255</v>
       </c>
       <c r="E98">
-        <v>1451.616</v>
+        <v>1476.787</v>
       </c>
       <c r="F98">
-        <v>2416.416</v>
+        <v>2441.587</v>
       </c>
       <c r="G98">
         <v>105.7</v>
@@ -9317,37 +9317,37 @@
         <v>253.886</v>
       </c>
       <c r="M98">
-        <v>485.2163328</v>
+        <v>490.2706696</v>
       </c>
       <c r="N98">
-        <v>-231.3303328</v>
+        <v>-236.3846696</v>
       </c>
       <c r="O98">
-        <v>-34.69954992</v>
+        <v>-35.45770044</v>
       </c>
       <c r="P98">
-        <v>-196.63078288</v>
+        <v>-200.92696916</v>
       </c>
       <c r="Q98">
-        <v>-196.14178288</v>
+        <v>-200.43796916</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.04987243826632</v>
+        <v>1.38456325102176</v>
       </c>
       <c r="T98">
-        <v>13.08642982411289</v>
+        <v>17.44857309881719</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.0784864346594394</v>
+        <v>0.07767729615779569</v>
       </c>
       <c r="W98">
-        <v>0.1850399239203846</v>
+        <v>0.1852023989315146</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.523242897729596</v>
+        <v>0.5178486410519713</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.221183224494222</v>
+        <v>0.222733224494222</v>
       </c>
       <c r="C99">
-        <v>-1644.396451813274</v>
+        <v>-1675.625162866432</v>
       </c>
       <c r="D99">
-        <v>691.4905481867255</v>
+        <v>685.4328371335681</v>
       </c>
       <c r="E99">
-        <v>1476.787</v>
+        <v>1501.958</v>
       </c>
       <c r="F99">
-        <v>2441.587</v>
+        <v>2466.758</v>
       </c>
       <c r="G99">
         <v>105.7</v>
@@ -9399,37 +9399,37 @@
         <v>253.886</v>
       </c>
       <c r="M99">
-        <v>490.2706696</v>
+        <v>495.3250063999999</v>
       </c>
       <c r="N99">
-        <v>-236.3846696</v>
+        <v>-241.4390064</v>
       </c>
       <c r="O99">
-        <v>-35.45770044</v>
+        <v>-36.21585095999999</v>
       </c>
       <c r="P99">
-        <v>-200.92696916</v>
+        <v>-205.22315544</v>
       </c>
       <c r="Q99">
-        <v>-200.43796916</v>
+        <v>-204.73415544</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.38456325102176</v>
+        <v>2.053944876532639</v>
       </c>
       <c r="T99">
-        <v>17.44857309881719</v>
+        <v>26.17285964822578</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.07767729615779569</v>
+        <v>0.07688467068679779</v>
       </c>
       <c r="W99">
-        <v>0.1852023989315146</v>
+        <v>0.185361558126091</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5178486410519713</v>
+        <v>0.5125644712453186</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.222733224494222</v>
+        <v>0.224283224494222</v>
       </c>
       <c r="C100">
-        <v>-1675.625162866432</v>
+        <v>-1706.748660086088</v>
       </c>
       <c r="D100">
-        <v>685.4328371335681</v>
+        <v>679.4803399139126</v>
       </c>
       <c r="E100">
-        <v>1501.958</v>
+        <v>1527.129</v>
       </c>
       <c r="F100">
-        <v>2466.758</v>
+        <v>2491.929</v>
       </c>
       <c r="G100">
         <v>105.7</v>
@@ -9481,37 +9481,37 @@
         <v>253.886</v>
       </c>
       <c r="M100">
-        <v>495.3250063999999</v>
+        <v>500.3793432000001</v>
       </c>
       <c r="N100">
-        <v>-241.4390064</v>
+        <v>-246.4933432000001</v>
       </c>
       <c r="O100">
-        <v>-36.21585095999999</v>
+        <v>-36.97400148000001</v>
       </c>
       <c r="P100">
-        <v>-205.22315544</v>
+        <v>-209.5193417200001</v>
       </c>
       <c r="Q100">
-        <v>-204.73415544</v>
+        <v>-209.0303417200001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.053944876532639</v>
+        <v>4.062089753065279</v>
       </c>
       <c r="T100">
-        <v>26.17285964822578</v>
+        <v>52.34571929645157</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.07688467068679779</v>
+        <v>0.07610805785157759</v>
       </c>
       <c r="W100">
-        <v>0.185361558126091</v>
+        <v>0.1855175019834032</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5125644712453186</v>
+        <v>0.5073870523438506</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.224283224494222</v>
-      </c>
-      <c r="C101">
-        <v>-1706.748660086088</v>
-      </c>
-      <c r="D101">
-        <v>679.4803399139126</v>
-      </c>
-      <c r="E101">
-        <v>1527.129</v>
-      </c>
-      <c r="F101">
-        <v>2491.929</v>
-      </c>
-      <c r="G101">
-        <v>105.7</v>
-      </c>
-      <c r="H101">
-        <v>1552.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>254.375</v>
-      </c>
-      <c r="K101">
-        <v>0.489</v>
-      </c>
-      <c r="L101">
-        <v>253.886</v>
-      </c>
-      <c r="M101">
-        <v>500.3793432000001</v>
-      </c>
-      <c r="N101">
-        <v>-246.4933432000001</v>
-      </c>
-      <c r="O101">
-        <v>-36.97400148000001</v>
-      </c>
-      <c r="P101">
-        <v>-209.5193417200001</v>
-      </c>
-      <c r="Q101">
-        <v>-209.0303417200001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.062089753065279</v>
-      </c>
-      <c r="T101">
-        <v>52.34571929645157</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.07610805785157759</v>
-      </c>
-      <c r="W101">
-        <v>0.1855175019834032</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5073870523438506</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
